--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - Medent.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - Medent.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="5"/>
+    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="709" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Medent" sheetId="11" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="446">
   <si>
     <t>Medent CCDA</t>
   </si>
@@ -103,7 +103,12 @@
   <si>
     <t>"meta" : {
     "lastUpdated" : "2024-02-23T00:00:00Z",
-    "profile" : ["http://shinny.org/us/ny/hrsn/StructureDefinition/SHINNYBundleProfile"]
+    "profile" : ["http://shinny.org/us/ny/hrsn/StructureDefinition/SHINNYBundleProfile"],
+    "security": [ {
+                  "code": "ETH",
+                  "system": "http://terminology.hl7.org/CodeSystem/v3-ActCode",
+                  "display": "Substance abuse information sensitivity"
+              } ]
   },</t>
   </si>
   <si>
@@ -113,6 +118,56 @@
     <t>"http://shinny.org/us/ny/hrsn/StructureDefinition/SHINNYBundleProfile"</t>
   </si>
   <si>
+    <t>meta -&gt; security</t>
+  </si>
+  <si>
+    <r>
+      <t>If the header variable `</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X-TechBD-Part2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>` has the value '</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>True</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>', then only the meta -&gt; security will be added.</t>
+    </r>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
@@ -128,7 +183,7 @@
     <t>entry</t>
   </si>
   <si>
-    <t>Resources - Patient, Encounter, Organization, Consent, Sexual orientation Observation , Observations, Grouper Observation</t>
+    <t>Resources - Patient, Encounter, Organization, Consent, Sexual orientation, Observations, Grouper Observation, Location</t>
   </si>
   <si>
     <t>FHIR Resources</t>
@@ -360,6 +415,12 @@
   </si>
   <si>
     <t>Observation (Observation Grouper)</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>The Location details are taken from the first occurance of the ClinicalDocument.component.structuredBody.component.section[code[@code='46240-8']].entry[1].encounter.participant.participantRole.</t>
   </si>
   <si>
     <t>Remarks</t>
@@ -3987,6 +4048,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Combine the Facility ID obtained from the header variable '</t>
     </r>
     <r>
@@ -5074,9 +5142,6 @@
     <t>Included references to all the Observation resources.</t>
   </si>
   <si>
-    <t>Location</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -5211,7 +5276,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5293,6 +5358,12 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -5441,6 +5512,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -5449,30 +5527,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5502,6 +5557,22 @@
       <color rgb="FF00B050"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
@@ -5836,16 +5907,13 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5854,119 +5922,122 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6024,9 +6095,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -6043,6 +6111,21 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -6591,20 +6674,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="8.88571428571429" style="26"/>
-    <col min="2" max="2" width="35.2190476190476" customWidth="1"/>
-    <col min="3" max="3" width="92.6666666666667" customWidth="1"/>
+    <col min="1" max="1" width="8.88181818181818" style="30"/>
+    <col min="2" max="2" width="35.2181818181818" customWidth="1"/>
+    <col min="3" max="3" width="92.6636363636364" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="31" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="26">
+      <c r="A3" s="30">
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -6615,7 +6698,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="26">
+      <c r="A4" s="30">
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -6626,7 +6709,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="26">
+      <c r="A5" s="30">
         <v>3</v>
       </c>
       <c r="B5" s="17" t="s">
@@ -6637,10 +6720,10 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="26">
+      <c r="A6" s="30">
         <v>4</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="24" t="s">
         <v>3</v>
       </c>
       <c r="C6" t="s">
@@ -6648,10 +6731,10 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="26">
+      <c r="A7" s="30">
         <v>5</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="32" t="s">
         <v>3</v>
       </c>
       <c r="C7" t="s">
@@ -6668,14 +6751,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="63.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="70.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="52.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="57.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="30.8545454545455" customWidth="1"/>
+    <col min="3" max="3" width="63.4272727272727" customWidth="1"/>
+    <col min="4" max="4" width="70.7181818181818" customWidth="1"/>
+    <col min="5" max="5" width="52.4272727272727" customWidth="1"/>
+    <col min="6" max="6" width="57.5727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -6692,18 +6775,18 @@
         <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" customFormat="1" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>422</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -6714,10 +6797,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" ht="60" spans="2:7">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="58" spans="2:7">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -6726,7 +6809,7 @@
       </c>
       <c r="D4"/>
       <c r="E4" s="6" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -6736,142 +6819,142 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D5"/>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D6"/>
       <c r="E6" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="2:6">
       <c r="B7" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D7" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" customFormat="1" ht="120" spans="2:5">
+    <row r="8" customFormat="1" ht="116" spans="2:5">
       <c r="B8" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" ht="60" spans="2:5">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" ht="58" spans="2:5">
       <c r="B9" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="4"/>
     </row>
     <row r="10" customFormat="1" spans="2:5">
       <c r="B10" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="4"/>
     </row>
     <row r="11" customFormat="1" spans="2:5">
       <c r="B11" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="4"/>
     </row>
     <row r="12" customFormat="1" spans="2:5">
       <c r="B12" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="4"/>
     </row>
     <row r="13" customFormat="1" spans="2:5">
       <c r="B13" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="4"/>
     </row>
     <row r="14" customFormat="1" spans="2:5">
       <c r="B14" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="4"/>
     </row>
     <row r="15" customFormat="1" spans="2:5">
       <c r="B15" s="4" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="4"/>
     </row>
     <row r="16" customFormat="1" spans="2:6">
       <c r="B16" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="4"/>
     </row>
     <row r="17" customFormat="1" ht="60" customHeight="1" spans="2:6">
       <c r="B17" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="8"/>
@@ -6891,15 +6974,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="28.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="65.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="46.2190476190476" customWidth="1"/>
-    <col min="5" max="5" width="61.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="46.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="28.3363636363636" customWidth="1"/>
+    <col min="3" max="3" width="65.6636363636364" customWidth="1"/>
+    <col min="4" max="4" width="46.2181818181818" customWidth="1"/>
+    <col min="5" max="5" width="61.2818181818182" customWidth="1"/>
+    <col min="6" max="6" width="46.2818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -6927,7 +7010,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" customFormat="1" spans="1:3">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
         <v>14</v>
@@ -6936,7 +7019,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" customFormat="1" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
         <v>16</v>
@@ -6948,116 +7031,139 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" ht="90" spans="2:4">
-      <c r="B5" t="s">
+    <row r="5" s="25" customFormat="1" ht="61" customHeight="1" spans="1:4">
+      <c r="A5" s="26"/>
+      <c r="B5" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="27" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
-      <c r="B6" t="s">
+    <row r="6" s="25" customFormat="1" ht="49" customHeight="1" spans="1:4">
+      <c r="A6" s="26"/>
+      <c r="B6" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="2:4">
-      <c r="B7" t="s">
+      <c r="D6" s="27"/>
+    </row>
+    <row r="7" s="25" customFormat="1" ht="86" customHeight="1" spans="1:4">
+      <c r="A7" s="26"/>
+      <c r="B7" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="2:3">
+      <c r="D7" s="27"/>
+    </row>
+    <row r="8" customFormat="1" spans="2:4">
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" ht="30" spans="2:3">
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" customFormat="1" spans="2:3">
       <c r="B9" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" ht="29" spans="2:3">
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="B15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" ht="75" spans="2:3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" ht="72.5" spans="2:3">
       <c r="B16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="2:3">
       <c r="B17" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" ht="150" spans="2:5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" ht="116" spans="2:5">
       <c r="B18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" ht="45" spans="2:5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" ht="29" spans="2:5">
       <c r="B19" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E19" s="10"/>
     </row>
-    <row r="20" ht="45" spans="2:5">
+    <row r="20" ht="43.5" spans="2:5">
       <c r="B20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E20" s="10"/>
     </row>
-    <row r="21" ht="30" spans="2:5">
+    <row r="21" ht="29" spans="2:5">
       <c r="B21" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E21" s="8"/>
     </row>
+    <row r="22" ht="43.5" spans="2:3">
+      <c r="B22" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D5:D7"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" display="&quot;http://shinny.org/us/ny/hrsn/StructureDefinition/SHINNYBundleProfile&quot;"/>
   </hyperlinks>
@@ -7070,13 +7176,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F68"/>
-  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="41.7809523809524" style="4" customWidth="1"/>
-    <col min="3" max="3" width="63.8857142857143" style="4" customWidth="1"/>
-    <col min="4" max="4" width="81.2857142857143" style="4" customWidth="1"/>
-    <col min="5" max="5" width="48.4285714285714" style="4" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="41.7818181818182" style="4" customWidth="1"/>
+    <col min="3" max="3" width="63.8818181818182" style="4" customWidth="1"/>
+    <col min="4" max="4" width="81.2818181818182" style="4" customWidth="1"/>
+    <col min="5" max="5" width="48.4272727272727" style="4" customWidth="1"/>
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7084,25 +7190,25 @@
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>46</v>
+      <c r="E1" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7111,7 +7217,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="2:4">
@@ -7122,7 +7228,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7131,7 +7237,7 @@
         <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3">
@@ -7139,658 +7245,658 @@
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" ht="30" spans="2:4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" ht="29" spans="2:4">
       <c r="B7" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" ht="60" spans="2:5">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" ht="58" spans="2:5">
       <c r="B8" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="B9" s="10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D9" s="10"/>
     </row>
     <row r="10" spans="2:4">
       <c r="B10" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="B11" s="15" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="B12" s="15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" ht="60" spans="2:4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" ht="58" spans="2:4">
       <c r="B13" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" ht="30" spans="2:4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" ht="29" spans="2:4">
       <c r="B14" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15" ht="30" spans="2:4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" ht="29" spans="2:4">
       <c r="B15" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="B16" s="15" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" ht="120" spans="2:5">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" ht="116" spans="2:5">
       <c r="B17" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" ht="60" spans="2:4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" ht="58" spans="2:4">
       <c r="B18" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D18" s="12"/>
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D19" s="12"/>
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D20" s="12"/>
     </row>
     <row r="21" spans="2:4">
       <c r="B21" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D21" s="12"/>
     </row>
     <row r="22" spans="2:4">
       <c r="B22" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D22" s="12"/>
     </row>
     <row r="23" spans="2:4">
       <c r="B23" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D23" s="12"/>
     </row>
     <row r="24" ht="48" customHeight="1" spans="2:5">
       <c r="B24" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="B25" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" ht="198" customHeight="1" spans="2:5">
       <c r="B26" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" ht="45" spans="2:5">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" ht="43.5" spans="2:5">
       <c r="B27" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" ht="30" spans="2:5">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
       <c r="B28" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="8"/>
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" ht="30" spans="2:5">
+    <row r="30" spans="2:5">
       <c r="B30" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="8"/>
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" ht="45" spans="2:5">
+    <row r="32" ht="43.5" spans="2:5">
       <c r="B32" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="33" ht="30" spans="2:4">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
       <c r="B33" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D33" s="14"/>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D34" s="14"/>
     </row>
-    <row r="35" ht="30" spans="2:4">
+    <row r="35" spans="2:4">
       <c r="B35" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D35" s="14"/>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D36" s="14"/>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="38" ht="45" spans="2:5">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" ht="43.5" spans="2:5">
       <c r="B38" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D38" s="14"/>
-      <c r="E38" s="29" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="39" ht="120" spans="2:6">
+      <c r="E38" s="33" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="39" ht="116" spans="2:6">
       <c r="B39" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="40" ht="120" spans="2:6">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" ht="116" spans="2:6">
       <c r="B40" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="15" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D41" s="10"/>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="15" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D42" s="10"/>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="15" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D43" s="10"/>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" ht="195" spans="2:5">
+    <row r="45" ht="188.5" spans="2:5">
       <c r="B45" s="15" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="46" ht="195" spans="2:5">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" ht="188.5" spans="2:5">
       <c r="B46" s="15" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="47" ht="195" spans="2:5">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="47" ht="188.5" spans="2:5">
       <c r="B47" s="15" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E47" s="24"/>
+        <v>153</v>
+      </c>
+      <c r="E47" s="23"/>
     </row>
     <row r="48" customFormat="1" spans="2:5">
       <c r="B48" s="4" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="4"/>
     </row>
     <row r="49" customFormat="1" spans="2:5">
       <c r="B49" s="4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D49" s="10"/>
       <c r="E49" s="4"/>
     </row>
     <row r="50" customFormat="1" spans="2:5">
       <c r="B50" s="4" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="4"/>
     </row>
     <row r="51" customFormat="1" spans="2:5">
       <c r="B51" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D51" s="10"/>
       <c r="E51" s="4"/>
     </row>
-    <row r="52" ht="150" spans="2:5">
+    <row r="52" ht="145" spans="2:5">
       <c r="B52" s="10" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D53" s="10"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54" customFormat="1" spans="2:5">
       <c r="B54" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D54" s="10"/>
       <c r="E54" s="8"/>
     </row>
     <row r="55" customFormat="1" spans="2:5">
       <c r="B55" s="4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D55" s="10"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56" customFormat="1" spans="2:5">
       <c r="B56" s="4" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D56" s="10"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57" customFormat="1" spans="2:5">
       <c r="B57" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D57" s="10"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D58" s="10"/>
       <c r="E58" s="8"/>
     </row>
-    <row r="59" ht="180" spans="2:5">
+    <row r="59" ht="174" spans="2:5">
       <c r="B59" s="10" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="60" ht="255" spans="2:6">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="60" ht="246.5" spans="2:6">
       <c r="B60" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D61" s="10"/>
       <c r="F61" s="4"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D62" s="10"/>
       <c r="F62" s="4"/>
     </row>
-    <row r="63" ht="210" spans="2:6">
+    <row r="63" ht="203" spans="2:6">
       <c r="B63" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D63" s="10"/>
       <c r="E63" s="13" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F63" s="4"/>
     </row>
     <row r="64" ht="56" customHeight="1" spans="2:6">
       <c r="B64" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="65" ht="43" customHeight="1" spans="2:4">
       <c r="B65" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D65" s="12"/>
     </row>
     <row r="66" ht="40" customHeight="1" spans="2:4">
       <c r="B66" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D66" s="12"/>
     </row>
     <row r="67" spans="2:4">
       <c r="B67" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="68" ht="43" customHeight="1" spans="2:4">
       <c r="B68" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D68" s="14"/>
     </row>
@@ -7813,14 +7919,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="63.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="70.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="52.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="57.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="30.8545454545455" customWidth="1"/>
+    <col min="3" max="3" width="63.4272727272727" customWidth="1"/>
+    <col min="4" max="4" width="70.7181818181818" customWidth="1"/>
+    <col min="5" max="5" width="52.4272727272727" customWidth="1"/>
+    <col min="6" max="6" width="57.5727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -7837,18 +7943,18 @@
         <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" ht="33" customHeight="1" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -7859,10 +7965,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="4" ht="60" spans="2:7">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" ht="58" spans="2:7">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -7870,7 +7976,7 @@
         <v>17</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -7880,7 +7986,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E5" s="8"/>
     </row>
@@ -7889,210 +7995,210 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>197</v>
-      </c>
-      <c r="E6" s="25"/>
-    </row>
-    <row r="7" ht="120" spans="2:6">
+        <v>201</v>
+      </c>
+      <c r="E6" s="24"/>
+    </row>
+    <row r="7" ht="116" spans="2:6">
       <c r="B7" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D7" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F7" s="4"/>
     </row>
     <row r="8" ht="94" customHeight="1" spans="2:5">
       <c r="B8" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C8" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="2:5">
       <c r="B9" s="5" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="8" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="8" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="11" ht="225" spans="2:5">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" ht="203" spans="2:5">
       <c r="B11" s="5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C11" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C12" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C13" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="14" ht="30" spans="2:5">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" ht="29" spans="2:5">
       <c r="B14" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C14" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D14" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15" ht="120" spans="2:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="15" ht="101.5" spans="2:5">
       <c r="B15" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="16" ht="45" spans="2:5">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="16" ht="43.5" spans="2:5">
       <c r="B16" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C16" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" ht="45" spans="2:5">
+    <row r="17" ht="43.5" spans="2:5">
       <c r="B17" s="5" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C17" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" ht="45" spans="2:5">
+    <row r="18" ht="43.5" spans="2:5">
       <c r="B18" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C18" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="19" ht="60" spans="2:5">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="19" ht="58" spans="2:5">
       <c r="B19" s="5" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C19" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="2:5">
       <c r="B20" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C20" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="8" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="2:6">
       <c r="B21" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="4"/>
     </row>
     <row r="22" customFormat="1" ht="60" customHeight="1" spans="2:6">
       <c r="B22" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="8"/>
@@ -8113,14 +8219,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="35.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="42.2857142857143" style="4" customWidth="1"/>
-    <col min="4" max="4" width="73.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="35.1454545454545" customWidth="1"/>
+    <col min="3" max="3" width="42.2818181818182" style="4" customWidth="1"/>
+    <col min="4" max="4" width="73.5727272727273" customWidth="1"/>
     <col min="5" max="5" width="53" customWidth="1"/>
-    <col min="6" max="6" width="51.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="51.7181818181818" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8130,7 +8236,7 @@
       <c r="B1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="22" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -8145,10 +8251,10 @@
     </row>
     <row r="2" ht="17" customHeight="1" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -8159,10 +8265,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="4" ht="60" spans="1:5">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4" ht="58" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -8171,10 +8277,10 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
@@ -8183,226 +8289,226 @@
         <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" ht="165" spans="2:5">
+    <row r="7" ht="159.5" spans="2:5">
       <c r="B7" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D7" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" ht="71" customHeight="1" spans="2:5">
       <c r="B8" s="5" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" ht="30" spans="2:5">
+    <row r="9" ht="29" spans="2:5">
       <c r="B9" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D9" s="10"/>
-      <c r="E9" s="24"/>
+      <c r="E9" s="23"/>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" ht="30" spans="2:4">
+    <row r="11" ht="29" spans="2:4">
       <c r="B11" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="12" ht="60" spans="2:5">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="12" ht="58" spans="2:5">
       <c r="B12" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="13" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" ht="33" customHeight="1" spans="2:4">
       <c r="B13" s="5" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D13" s="12"/>
     </row>
     <row r="14" customFormat="1" spans="2:3">
       <c r="B14" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" ht="60" spans="2:4">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="58" spans="2:4">
       <c r="B15" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C15" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" ht="30" spans="2:3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" ht="29" spans="2:3">
       <c r="B16" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="17" ht="60" spans="2:4">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="17" ht="58" spans="2:4">
       <c r="B17" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="19" ht="45" spans="2:5">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="19" ht="43.5" spans="2:5">
       <c r="B19" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E20" s="17"/>
     </row>
     <row r="21" ht="409.5" spans="2:5">
       <c r="B21" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="22" ht="60" spans="2:5">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="22" ht="58" spans="2:5">
       <c r="B22" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="E22" s="22"/>
+        <v>288</v>
+      </c>
+      <c r="E22" s="21"/>
     </row>
     <row r="23" ht="66" customHeight="1" spans="2:5">
       <c r="B23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C23" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E23" s="4"/>
     </row>
     <row r="24" customFormat="1" spans="2:5">
       <c r="B24" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="4"/>
     </row>
     <row r="25" customFormat="1" spans="2:4">
       <c r="B25" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" customFormat="1" ht="46" customHeight="1" spans="2:4">
       <c r="B26" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D26" s="14"/>
     </row>
@@ -8424,14 +8530,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="27.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="50.8857142857143" customWidth="1"/>
-    <col min="4" max="4" width="72.8571428571429" customWidth="1"/>
-    <col min="5" max="5" width="46.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="45.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="27.3363636363636" customWidth="1"/>
+    <col min="3" max="3" width="50.8818181818182" customWidth="1"/>
+    <col min="4" max="4" width="72.8545454545455" customWidth="1"/>
+    <col min="5" max="5" width="46.4272727272727" customWidth="1"/>
+    <col min="6" max="6" width="45.7181818181818" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8448,15 +8554,15 @@
         <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" customFormat="1" spans="2:3">
@@ -8464,7 +8570,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="2:3">
@@ -8481,20 +8587,20 @@
         <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -8502,270 +8608,270 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="5" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D7" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" ht="63" customHeight="1" spans="2:6">
       <c r="B8" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>302</v>
+        <v>305</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" ht="30" spans="2:5">
+    <row r="10" ht="29" spans="2:5">
       <c r="B10" s="4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" ht="30" spans="2:5">
+    <row r="11" ht="29" spans="2:5">
       <c r="B11" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="30" spans="2:5">
+    <row r="12" ht="29" spans="2:5">
       <c r="B12" s="4" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="8"/>
     </row>
     <row r="13" customFormat="1" ht="66" customHeight="1" spans="2:6">
       <c r="B13" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>302</v>
+        <v>316</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="2:5">
       <c r="B14" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D14" s="10"/>
-      <c r="E14" s="22"/>
-    </row>
-    <row r="15" customFormat="1" ht="30" spans="2:5">
+      <c r="E14" s="21"/>
+    </row>
+    <row r="15" customFormat="1" ht="29" spans="2:5">
       <c r="B15" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D15" s="10"/>
-      <c r="E15" s="22"/>
-    </row>
-    <row r="16" customFormat="1" ht="30" spans="2:5">
+      <c r="E15" s="21"/>
+    </row>
+    <row r="16" customFormat="1" ht="29" spans="2:5">
       <c r="B16" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" customFormat="1" ht="30" spans="2:4">
+    <row r="17" customFormat="1" ht="29" spans="2:4">
       <c r="B17" s="4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D17" s="10"/>
     </row>
-    <row r="18" ht="60" spans="2:5">
+    <row r="18" ht="58" spans="2:5">
       <c r="B18" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="19" ht="93" customHeight="1" spans="2:6">
       <c r="B19" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="2:6">
       <c r="B20" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="10"/>
       <c r="F20" s="8" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="21" customFormat="1" ht="50" customHeight="1" spans="2:6">
       <c r="B21" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="10" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" customFormat="1" ht="30" spans="2:6">
+    <row r="22" customFormat="1" ht="29" spans="2:6">
       <c r="B22" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D22" s="10"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" customFormat="1" ht="195" spans="2:6">
+    <row r="23" customFormat="1" ht="188.5" spans="2:6">
       <c r="B23" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="13" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" customFormat="1" ht="120" spans="2:6">
+    <row r="24" customFormat="1" ht="116" spans="2:6">
       <c r="B24" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" customFormat="1" ht="30" spans="2:6">
+    <row r="25" customFormat="1" ht="29" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" customFormat="1" ht="30" spans="2:6">
+    <row r="26" customFormat="1" ht="29" spans="2:6">
       <c r="B26" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" customFormat="1" ht="30" spans="2:6">
+    <row r="27" customFormat="1" ht="29" spans="2:6">
       <c r="B27" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" customFormat="1" ht="30" spans="2:6">
+    <row r="28" customFormat="1" ht="29" spans="2:6">
       <c r="B28" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" customFormat="1" ht="30" spans="2:6">
+    <row r="29" customFormat="1" ht="29" spans="2:6">
       <c r="B29" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" customFormat="1" ht="30" spans="2:6">
+    <row r="30" customFormat="1" ht="29" spans="2:6">
       <c r="B30" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="4"/>
@@ -8773,21 +8879,21 @@
     </row>
     <row r="31" customFormat="1" spans="2:4">
       <c r="B31" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" customFormat="1" ht="46" customHeight="1" spans="2:4">
       <c r="B32" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D32" s="14"/>
     </row>
@@ -8809,13 +8915,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="33.8857142857143" customWidth="1"/>
-    <col min="3" max="3" width="46.8571428571429" customWidth="1"/>
-    <col min="4" max="4" width="57.1142857142857" customWidth="1"/>
-    <col min="5" max="5" width="54.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="33.8818181818182" customWidth="1"/>
+    <col min="3" max="3" width="46.8545454545455" customWidth="1"/>
+    <col min="4" max="4" width="57.1181818181818" customWidth="1"/>
+    <col min="5" max="5" width="54.7181818181818" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8833,15 +8939,15 @@
         <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" ht="45" spans="1:1">
-      <c r="A2" s="21" t="s">
-        <v>342</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" ht="43.5" spans="1:1">
+      <c r="A2" s="20" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8850,7 +8956,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -8862,7 +8968,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8871,18 +8977,18 @@
         <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" ht="30" spans="2:6">
+    <row r="6" ht="29" spans="2:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -8890,161 +8996,161 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="8" ht="150" spans="2:5">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" ht="145" spans="2:5">
       <c r="B8" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D8" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" ht="70" customHeight="1" spans="2:4">
       <c r="B9" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="10" ht="30" spans="2:4">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="10" ht="29" spans="2:4">
       <c r="B10" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D10" s="10"/>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="30" spans="2:4">
+    <row r="12" ht="29" spans="2:4">
       <c r="B12" s="5" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D12" s="10"/>
     </row>
     <row r="13" ht="38" customHeight="1" spans="2:4">
       <c r="B13" s="4" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="14" ht="30" spans="2:4">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="14" ht="29" spans="2:4">
       <c r="B14" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D14" s="10"/>
     </row>
     <row r="15" ht="153" customHeight="1" spans="2:5">
       <c r="B15" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="8" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="16" ht="75" spans="2:4">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="16" ht="58" spans="2:4">
       <c r="B16" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C16" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="17" ht="30" spans="2:3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17" ht="29" spans="2:3">
       <c r="B17" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="18" ht="90" spans="2:5">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="18" ht="87" spans="2:5">
       <c r="B18" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D18" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D19" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1" spans="2:4">
       <c r="B21" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D21" s="14"/>
     </row>
@@ -9063,14 +9169,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="34.5714285714286" customWidth="1"/>
-    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="56.552380952381" customWidth="1"/>
-    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="50.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="34.5727272727273" customWidth="1"/>
+    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
+    <col min="4" max="4" width="56.5545454545455" customWidth="1"/>
+    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
+    <col min="6" max="6" width="50.2818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -9087,18 +9193,18 @@
         <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" ht="17" customHeight="1" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -9111,19 +9217,19 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="4" ht="78" spans="1:4">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="4" ht="82.5" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>375</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>376</v>
+        <v>379</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
@@ -9132,18 +9238,18 @@
         <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -9151,268 +9257,268 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="8" ht="150" spans="2:5">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" ht="145" spans="2:5">
       <c r="B8" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D8" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" ht="139" customHeight="1" spans="2:5">
       <c r="B9" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="10" ht="45" spans="2:5">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="10" ht="43.5" spans="2:5">
       <c r="B10" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="8" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="11" ht="210" spans="2:5">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="11" ht="203" spans="2:5">
       <c r="B11" s="5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="11" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="12" ht="210" spans="2:5">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="12" ht="203" spans="2:5">
       <c r="B12" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="11" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="8" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14" ht="84" customHeight="1" spans="2:5">
       <c r="B14" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E14" s="9"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="9"/>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="9"/>
     </row>
-    <row r="17" ht="30" spans="2:5">
+    <row r="17" ht="29" spans="2:5">
       <c r="B17" s="5" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="8" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="18" ht="105" spans="2:5">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="18" ht="101.5" spans="2:5">
       <c r="B18" s="4" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="19" ht="30" spans="2:3">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="19" ht="29" spans="2:3">
       <c r="B19" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="20" ht="30" spans="2:3">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="20" ht="29" spans="2:3">
       <c r="B20" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C20" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" ht="37" customHeight="1" spans="2:5">
       <c r="B21" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" ht="75" spans="2:5">
+    <row r="22" ht="72.5" spans="2:5">
       <c r="B22" s="5" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C22" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D22" s="12"/>
-      <c r="E22" s="20" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="23" ht="45" spans="2:5">
+      <c r="E22" s="19" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="23" ht="43.5" spans="2:5">
       <c r="B23" s="5" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="11" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="24" ht="75" spans="2:4">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="24" ht="58" spans="2:4">
       <c r="B24" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C24" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="25" ht="30" spans="2:3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="25" ht="29" spans="2:3">
       <c r="B25" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="26" ht="45" spans="2:4">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="26" ht="43.5" spans="2:4">
       <c r="B26" s="5" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C26" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="27" ht="210" spans="2:5">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="27" ht="188.5" spans="2:5">
       <c r="B27" s="5" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="28" ht="45" spans="2:4">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="28" ht="43.5" spans="2:4">
       <c r="B28" s="5" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D29" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="30" spans="2:4">
       <c r="B30" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="31" ht="46" customHeight="1" spans="2:4">
       <c r="B31" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D31" s="14"/>
     </row>
@@ -9433,14 +9539,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="33.5714285714286" customWidth="1"/>
-    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="56.552380952381" customWidth="1"/>
-    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="47.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="33.5727272727273" customWidth="1"/>
+    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
+    <col min="4" max="4" width="56.5545454545455" customWidth="1"/>
+    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
+    <col min="6" max="6" width="47.5727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -9457,18 +9563,18 @@
         <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" ht="17" customHeight="1" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -9481,7 +9587,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -9493,7 +9599,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
@@ -9502,18 +9608,18 @@
         <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -9521,170 +9627,170 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="8" ht="150" spans="2:5">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" ht="145" spans="2:5">
       <c r="B8" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D8" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" ht="409" customHeight="1" spans="2:5">
       <c r="B9" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="10" ht="150" spans="2:5">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="10" ht="145" spans="2:5">
       <c r="B10" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="11" ht="180" spans="2:5">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="11" ht="159.5" spans="2:5">
       <c r="B11" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C11" s="4"/>
       <c r="E11" s="11" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="12" ht="150" spans="2:5">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="12" ht="145" spans="2:5">
       <c r="B12" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C12" s="4"/>
       <c r="E12" s="11" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="13" ht="75" spans="2:4">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="13" ht="58" spans="2:4">
       <c r="B13" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C13" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="14" ht="30" spans="2:3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="14" ht="29" spans="2:3">
       <c r="B14" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="15" ht="45" spans="2:4">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="15" ht="43.5" spans="2:4">
       <c r="B15" s="5" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C15" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="16" ht="210" spans="2:5">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="16" ht="188.5" spans="2:5">
       <c r="B16" s="5" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="17" ht="45" spans="2:4">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="17" ht="43.5" spans="2:4">
       <c r="B17" s="5" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D18" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="19" ht="165" spans="2:5">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="19" ht="159.5" spans="2:5">
       <c r="B19" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E19" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="21" ht="46" customHeight="1" spans="2:4">
       <c r="B21" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D21" s="14"/>
     </row>

--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - Medent.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - Medent.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="709" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Medent" sheetId="11" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="447">
   <si>
     <t>Medent CCDA</t>
   </si>
@@ -122,6 +122,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>If the header variable `</t>
     </r>
     <r>
@@ -624,13 +631,11 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-HP -&gt; home  
-H -&gt; home  
-WP -&gt; work  
-TMP -&gt; temp  
-OLD -&gt; old  
-BAD -&gt; old  
-All Others -&gt; patientRole.addr.use</t>
+WP, DIR, PUB -&gt; work
+BA -&gt; billing
+TMP -&gt; temp
+OLD, BAD -&gt; old
+All Others -&gt; home</t>
     </r>
   </si>
   <si>
@@ -721,18 +726,12 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-AS -&gt; work  
-DIR -&gt; work  
-PUB -&gt; work  
-WP -&gt; work  
-BAD -&gt; old  
-H -&gt; home  
-HP -&gt; home  
-HV -&gt; home  
-MC -&gt; mobile  
-PG -&gt; mobile  
-TMP -&gt; temp  
-All Others -&gt; patient.telecom.use</t>
+AS, DIR, PUB, WP, WPN -&gt; work
+H, HP, HV, PRN, ORN, PRS -&gt; home
+MC, PG -&gt; mobile
+TMP -&gt; temp
+BAD -&gt; old
+All others -&gt; home</t>
     </r>
   </si>
   <si>
@@ -3672,6 +3671,35 @@
     <t>Document.author.assignedAuthor.representedOrganization.telecom.use</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>telecom -&gt; use Mapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+AS, DIR, PUB, WP, WPN -&gt; work
+MC, PG -&gt; mobile
+TMP -&gt; temp
+BAD -&gt; old
+All others -&gt; work</t>
+    </r>
+  </si>
+  <si>
     <t>Document.author.assignedAuthor.representedOrganization.addr.streetAddressLine
 Document.author.assignedAuthor.representedOrganization.addr.city
 Document.author.assignedAuthor.representedOrganization.addr.state,
@@ -3690,6 +3718,35 @@
   </si>
   <si>
     <t>Document.author.assignedAuthor.representedOrganization.addr.use</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>addr.use -&gt; use Mapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+WP, DIR, PUB -&gt; work
+BA -&gt; billing
+TMP -&gt; temp
+OLD, BAD -&gt; old
+All Others -&gt; work</t>
+    </r>
   </si>
   <si>
     <t>Document.author.assignedAuthor.representedOrganization.addr.streetAddressLine</t>
@@ -5197,37 +5254,6 @@
   </si>
   <si>
     <t>addr.use</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>addr.use -&gt; use Mapping</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-HP -&gt; home  
-H -&gt; home  
-WP -&gt; work  
-TMP -&gt; temp  
-OLD -&gt; old  
-BAD -&gt; old  
-All Others -&gt;addr.use</t>
-    </r>
   </si>
   <si>
     <t>addr.streetAddressLine
@@ -5512,13 +5538,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -5527,7 +5546,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5562,14 +5596,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -6037,7 +6063,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6102,6 +6128,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6674,20 +6703,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="8.88181818181818" style="30"/>
-    <col min="2" max="2" width="35.2181818181818" customWidth="1"/>
-    <col min="3" max="3" width="92.6636363636364" customWidth="1"/>
+    <col min="1" max="1" width="8.88571428571429" style="31"/>
+    <col min="2" max="2" width="35.2190476190476" customWidth="1"/>
+    <col min="3" max="3" width="92.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="32" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="30">
+      <c r="A3" s="31">
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -6698,7 +6727,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="30">
+      <c r="A4" s="31">
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -6709,7 +6738,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="30">
+      <c r="A5" s="31">
         <v>3</v>
       </c>
       <c r="B5" s="17" t="s">
@@ -6720,10 +6749,10 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="30">
+      <c r="A6" s="31">
         <v>4</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="25" t="s">
         <v>3</v>
       </c>
       <c r="C6" t="s">
@@ -6731,10 +6760,10 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="30">
+      <c r="A7" s="31">
         <v>5</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="33" t="s">
         <v>3</v>
       </c>
       <c r="C7" t="s">
@@ -6751,14 +6780,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="30.8545454545455" customWidth="1"/>
-    <col min="3" max="3" width="63.4272727272727" customWidth="1"/>
-    <col min="4" max="4" width="70.7181818181818" customWidth="1"/>
-    <col min="5" max="5" width="52.4272727272727" customWidth="1"/>
-    <col min="6" max="6" width="57.5727272727273" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="63.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="70.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="52.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="57.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -6786,7 +6815,7 @@
         <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -6797,10 +6826,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" ht="58" spans="2:7">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="60" spans="2:7">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -6809,7 +6838,7 @@
       </c>
       <c r="D4"/>
       <c r="E4" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -6824,19 +6853,19 @@
       <c r="D5"/>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D6"/>
       <c r="E6" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="2:6">
@@ -6844,34 +6873,34 @@
         <v>324</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D7" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" customFormat="1" ht="116" spans="2:5">
+    <row r="8" customFormat="1" ht="90" spans="2:5">
       <c r="B8" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>86</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" ht="58" spans="2:5">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" ht="60" spans="2:5">
       <c r="B9" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="4"/>
@@ -6881,7 +6910,7 @@
         <v>90</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="4"/>
@@ -6891,7 +6920,7 @@
         <v>92</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="4"/>
@@ -6901,7 +6930,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="4"/>
@@ -6911,7 +6940,7 @@
         <v>96</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="4"/>
@@ -6921,17 +6950,17 @@
         <v>98</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="4"/>
     </row>
     <row r="15" customFormat="1" spans="2:5">
       <c r="B15" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="4"/>
@@ -6944,7 +6973,7 @@
         <v>193</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="4"/>
@@ -6954,7 +6983,7 @@
         <v>195</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="8"/>
@@ -6975,14 +7004,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="28.3363636363636" customWidth="1"/>
-    <col min="3" max="3" width="65.6636363636364" customWidth="1"/>
-    <col min="4" max="4" width="46.2181818181818" customWidth="1"/>
-    <col min="5" max="5" width="61.2818181818182" customWidth="1"/>
-    <col min="6" max="6" width="46.2818181818182" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="28.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="65.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="46.2190476190476" customWidth="1"/>
+    <col min="5" max="5" width="61.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="46.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -7031,37 +7060,37 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" s="25" customFormat="1" ht="61" customHeight="1" spans="1:4">
-      <c r="A5" s="26"/>
-      <c r="B5" s="26" t="s">
+    <row r="5" s="26" customFormat="1" ht="61" customHeight="1" spans="1:4">
+      <c r="A5" s="27"/>
+      <c r="B5" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="28" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" s="25" customFormat="1" ht="49" customHeight="1" spans="1:4">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26" t="s">
+    <row r="6" s="26" customFormat="1" ht="49" customHeight="1" spans="1:4">
+      <c r="A6" s="27"/>
+      <c r="B6" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="27"/>
-    </row>
-    <row r="7" s="25" customFormat="1" ht="86" customHeight="1" spans="1:4">
-      <c r="A7" s="26"/>
-      <c r="B7" s="26" t="s">
+      <c r="D6" s="28"/>
+    </row>
+    <row r="7" s="26" customFormat="1" ht="86" customHeight="1" spans="1:4">
+      <c r="A7" s="27"/>
+      <c r="B7" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="27"/>
+      <c r="D7" s="28"/>
     </row>
     <row r="8" customFormat="1" spans="2:4">
       <c r="B8" t="s">
@@ -7080,7 +7109,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="29" spans="2:3">
+    <row r="10" customFormat="1" ht="30" spans="2:3">
       <c r="B10" t="s">
         <v>30</v>
       </c>
@@ -7101,7 +7130,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" ht="72.5" spans="2:3">
+    <row r="16" ht="75" spans="2:3">
       <c r="B16" t="s">
         <v>35</v>
       </c>
@@ -7117,7 +7146,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" ht="116" spans="2:5">
+    <row r="18" ht="150" spans="2:5">
       <c r="B18" t="s">
         <v>39</v>
       </c>
@@ -7128,7 +7157,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" ht="29" spans="2:5">
+    <row r="19" ht="45" spans="2:5">
       <c r="B19" s="4" t="s">
         <v>42</v>
       </c>
@@ -7137,7 +7166,7 @@
       </c>
       <c r="E19" s="10"/>
     </row>
-    <row r="20" ht="43.5" spans="2:5">
+    <row r="20" ht="45" spans="2:5">
       <c r="B20" t="s">
         <v>44</v>
       </c>
@@ -7146,14 +7175,14 @@
       </c>
       <c r="E20" s="10"/>
     </row>
-    <row r="21" ht="29" spans="2:5">
+    <row r="21" ht="30" spans="2:5">
       <c r="B21" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" ht="43.5" spans="2:3">
-      <c r="B22" s="29" t="s">
+    <row r="22" ht="45" spans="2:3">
+      <c r="B22" s="30" t="s">
         <v>47</v>
       </c>
       <c r="C22" s="10" t="s">
@@ -7176,13 +7205,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F68"/>
-  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="41.7818181818182" style="4" customWidth="1"/>
-    <col min="3" max="3" width="63.8818181818182" style="4" customWidth="1"/>
-    <col min="4" max="4" width="81.2818181818182" style="4" customWidth="1"/>
-    <col min="5" max="5" width="48.4272727272727" style="4" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="41.7809523809524" style="4" customWidth="1"/>
+    <col min="3" max="3" width="63.8857142857143" style="4" customWidth="1"/>
+    <col min="4" max="4" width="81.2857142857143" style="4" customWidth="1"/>
+    <col min="5" max="5" width="48.4285714285714" style="4" customWidth="1"/>
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7190,19 +7219,19 @@
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="23" t="s">
         <v>50</v>
       </c>
     </row>
@@ -7248,7 +7277,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" ht="29" spans="2:4">
+    <row r="7" ht="30" spans="2:4">
       <c r="B7" s="4" t="s">
         <v>55</v>
       </c>
@@ -7259,7 +7288,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" ht="58" spans="2:5">
+    <row r="8" ht="60" spans="2:5">
       <c r="B8" s="4" t="s">
         <v>58</v>
       </c>
@@ -7315,7 +7344,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" ht="58" spans="2:4">
+    <row r="13" ht="60" spans="2:4">
       <c r="B13" s="4" t="s">
         <v>72</v>
       </c>
@@ -7326,7 +7355,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" ht="29" spans="2:4">
+    <row r="14" ht="30" spans="2:4">
       <c r="B14" s="4" t="s">
         <v>75</v>
       </c>
@@ -7337,7 +7366,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" ht="29" spans="2:4">
+    <row r="15" ht="30" spans="2:4">
       <c r="B15" s="4" t="s">
         <v>78</v>
       </c>
@@ -7359,7 +7388,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" ht="116" spans="2:5">
+    <row r="17" ht="90" spans="2:5">
       <c r="B17" s="4" t="s">
         <v>84</v>
       </c>
@@ -7373,7 +7402,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" ht="58" spans="2:4">
+    <row r="18" ht="60" spans="2:4">
       <c r="B18" s="4" t="s">
         <v>88</v>
       </c>
@@ -7446,18 +7475,18 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" ht="198" customHeight="1" spans="2:5">
+    <row r="26" ht="105" spans="2:5">
       <c r="B26" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="22" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="27" ht="43.5" spans="2:5">
+    <row r="27" ht="45" spans="2:5">
       <c r="B27" s="4" t="s">
         <v>108</v>
       </c>
@@ -7471,7 +7500,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="2:5">
+    <row r="28" ht="30" spans="2:5">
       <c r="B28" s="4" t="s">
         <v>112</v>
       </c>
@@ -7491,7 +7520,7 @@
       <c r="D29" s="14"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" spans="2:5">
+    <row r="30" ht="30" spans="2:5">
       <c r="B30" s="4" t="s">
         <v>116</v>
       </c>
@@ -7511,7 +7540,7 @@
       <c r="D31" s="14"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" ht="43.5" spans="2:5">
+    <row r="32" ht="45" spans="2:5">
       <c r="B32" s="4" t="s">
         <v>108</v>
       </c>
@@ -7525,7 +7554,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="2:4">
+    <row r="33" ht="30" spans="2:4">
       <c r="B33" s="4" t="s">
         <v>112</v>
       </c>
@@ -7543,7 +7572,7 @@
       </c>
       <c r="D34" s="14"/>
     </row>
-    <row r="35" spans="2:4">
+    <row r="35" ht="30" spans="2:4">
       <c r="B35" s="4" t="s">
         <v>116</v>
       </c>
@@ -7572,7 +7601,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="38" ht="43.5" spans="2:5">
+    <row r="38" ht="45" spans="2:5">
       <c r="B38" s="4" t="s">
         <v>128</v>
       </c>
@@ -7580,11 +7609,11 @@
         <v>79</v>
       </c>
       <c r="D38" s="14"/>
-      <c r="E38" s="33" t="s">
+      <c r="E38" s="34" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="39" ht="116" spans="2:6">
+    <row r="39" ht="120" spans="2:6">
       <c r="B39" s="4" t="s">
         <v>130</v>
       </c>
@@ -7595,7 +7624,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" ht="116" spans="2:6">
+    <row r="40" ht="120" spans="2:6">
       <c r="B40" s="4" t="s">
         <v>133</v>
       </c>
@@ -7642,7 +7671,7 @@
       </c>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" ht="188.5" spans="2:5">
+    <row r="45" ht="195" spans="2:5">
       <c r="B45" s="15" t="s">
         <v>143</v>
       </c>
@@ -7656,7 +7685,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="46" ht="188.5" spans="2:5">
+    <row r="46" ht="195" spans="2:5">
       <c r="B46" s="15" t="s">
         <v>147</v>
       </c>
@@ -7670,7 +7699,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" ht="188.5" spans="2:5">
+    <row r="47" ht="195" spans="2:5">
       <c r="B47" s="15" t="s">
         <v>151</v>
       </c>
@@ -7680,7 +7709,7 @@
       <c r="D47" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E47" s="23"/>
+      <c r="E47" s="24"/>
     </row>
     <row r="48" customFormat="1" spans="2:5">
       <c r="B48" s="4" t="s">
@@ -7722,7 +7751,7 @@
       <c r="D51" s="10"/>
       <c r="E51" s="4"/>
     </row>
-    <row r="52" ht="145" spans="2:5">
+    <row r="52" ht="150" spans="2:5">
       <c r="B52" s="10" t="s">
         <v>160</v>
       </c>
@@ -7796,7 +7825,7 @@
       <c r="D58" s="10"/>
       <c r="E58" s="8"/>
     </row>
-    <row r="59" ht="174" spans="2:5">
+    <row r="59" ht="180" spans="2:5">
       <c r="B59" s="10" t="s">
         <v>174</v>
       </c>
@@ -7810,7 +7839,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" ht="246.5" spans="2:6">
+    <row r="60" ht="255" spans="2:6">
       <c r="B60" s="4" t="s">
         <v>177</v>
       </c>
@@ -7841,7 +7870,7 @@
       <c r="D62" s="10"/>
       <c r="F62" s="4"/>
     </row>
-    <row r="63" ht="203" spans="2:6">
+    <row r="63" ht="210" spans="2:6">
       <c r="B63" s="4" t="s">
         <v>184</v>
       </c>
@@ -7919,14 +7948,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="30.8545454545455" customWidth="1"/>
-    <col min="3" max="3" width="63.4272727272727" customWidth="1"/>
-    <col min="4" max="4" width="70.7181818181818" customWidth="1"/>
-    <col min="5" max="5" width="52.4272727272727" customWidth="1"/>
-    <col min="6" max="6" width="57.5727272727273" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="63.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="70.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="52.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="57.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -7968,7 +7997,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" ht="58" spans="2:7">
+    <row r="4" ht="60" spans="2:7">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -7997,9 +8026,9 @@
       <c r="C6" t="s">
         <v>201</v>
       </c>
-      <c r="E6" s="24"/>
-    </row>
-    <row r="7" ht="116" spans="2:6">
+      <c r="E6" s="25"/>
+    </row>
+    <row r="7" ht="120" spans="2:6">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
@@ -8052,7 +8081,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="11" ht="203" spans="2:5">
+    <row r="11" ht="225" spans="2:5">
       <c r="B11" s="5" t="s">
         <v>214</v>
       </c>
@@ -8088,7 +8117,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" ht="29" spans="2:5">
+    <row r="14" ht="30" spans="2:5">
       <c r="B14" s="5" t="s">
         <v>221</v>
       </c>
@@ -8102,7 +8131,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="15" ht="101.5" spans="2:5">
+    <row r="15" ht="120" spans="2:5">
       <c r="B15" s="5" t="s">
         <v>225</v>
       </c>
@@ -8116,7 +8145,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="16" ht="43.5" spans="2:5">
+    <row r="16" ht="45" spans="2:5">
       <c r="B16" s="5" t="s">
         <v>229</v>
       </c>
@@ -8128,7 +8157,7 @@
       </c>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" ht="43.5" spans="2:5">
+    <row r="17" ht="45" spans="2:5">
       <c r="B17" s="5" t="s">
         <v>232</v>
       </c>
@@ -8140,7 +8169,7 @@
       </c>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" ht="43.5" spans="2:5">
+    <row r="18" ht="45" spans="2:5">
       <c r="B18" t="s">
         <v>235</v>
       </c>
@@ -8154,7 +8183,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="19" ht="58" spans="2:5">
+    <row r="19" ht="60" spans="2:5">
       <c r="B19" s="5" t="s">
         <v>238</v>
       </c>
@@ -8219,14 +8248,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="35.1454545454545" customWidth="1"/>
-    <col min="3" max="3" width="42.2818181818182" style="4" customWidth="1"/>
-    <col min="4" max="4" width="73.5727272727273" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="35.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="42.2857142857143" style="4" customWidth="1"/>
+    <col min="4" max="4" width="73.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="53" customWidth="1"/>
-    <col min="6" max="6" width="51.7181818181818" customWidth="1"/>
+    <col min="6" max="6" width="51.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8236,7 +8265,7 @@
       <c r="B1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="23" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -8268,7 +8297,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="4" ht="58" spans="1:5">
+    <row r="4" ht="60" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -8295,7 +8324,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
@@ -8306,7 +8335,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" ht="159.5" spans="2:5">
+    <row r="7" ht="165" spans="2:5">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
@@ -8332,7 +8361,7 @@
       </c>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" ht="29" spans="2:5">
+    <row r="9" ht="30" spans="2:5">
       <c r="B9" s="5" t="s">
         <v>256</v>
       </c>
@@ -8340,7 +8369,7 @@
         <v>257</v>
       </c>
       <c r="D9" s="10"/>
-      <c r="E9" s="23"/>
+      <c r="E9" s="24"/>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="5" t="s">
@@ -8352,7 +8381,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" ht="29" spans="2:4">
+    <row r="11" ht="30" spans="2:4">
       <c r="B11" s="5" t="s">
         <v>260</v>
       </c>
@@ -8363,7 +8392,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="12" ht="58" spans="2:5">
+    <row r="12" ht="60" spans="2:5">
       <c r="B12" s="5" t="s">
         <v>263</v>
       </c>
@@ -8389,7 +8418,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="58" spans="2:4">
+    <row r="15" customFormat="1" ht="60" spans="2:4">
       <c r="B15" s="5" t="s">
         <v>269</v>
       </c>
@@ -8400,7 +8429,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="29" spans="2:3">
+    <row r="16" customFormat="1" ht="30" spans="2:3">
       <c r="B16" s="5" t="s">
         <v>271</v>
       </c>
@@ -8408,7 +8437,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="17" ht="58" spans="2:4">
+    <row r="17" ht="60" spans="2:4">
       <c r="B17" t="s">
         <v>273</v>
       </c>
@@ -8427,7 +8456,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="19" ht="43.5" spans="2:5">
+    <row r="19" ht="45" spans="2:5">
       <c r="B19" t="s">
         <v>278</v>
       </c>
@@ -8461,7 +8490,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="22" ht="58" spans="2:5">
+    <row r="22" ht="60" spans="2:5">
       <c r="B22" t="s">
         <v>287</v>
       </c>
@@ -8530,14 +8559,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="27.3363636363636" customWidth="1"/>
-    <col min="3" max="3" width="50.8818181818182" customWidth="1"/>
-    <col min="4" max="4" width="72.8545454545455" customWidth="1"/>
-    <col min="5" max="5" width="46.4272727272727" customWidth="1"/>
-    <col min="6" max="6" width="45.7181818181818" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="27.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="50.8857142857143" customWidth="1"/>
+    <col min="4" max="4" width="72.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="46.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="45.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8595,7 +8624,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
@@ -8644,7 +8673,7 @@
       <c r="D9" s="10"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" ht="29" spans="2:5">
+    <row r="10" ht="30" spans="2:5">
       <c r="B10" s="4" t="s">
         <v>309</v>
       </c>
@@ -8654,7 +8683,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" ht="29" spans="2:5">
+    <row r="11" ht="30" spans="2:5">
       <c r="B11" s="4" t="s">
         <v>311</v>
       </c>
@@ -8664,7 +8693,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="29" spans="2:5">
+    <row r="12" ht="30" spans="2:5">
       <c r="B12" s="4" t="s">
         <v>312</v>
       </c>
@@ -8698,7 +8727,7 @@
       <c r="D14" s="10"/>
       <c r="E14" s="21"/>
     </row>
-    <row r="15" customFormat="1" ht="29" spans="2:5">
+    <row r="15" customFormat="1" ht="30" spans="2:5">
       <c r="B15" s="4" t="s">
         <v>319</v>
       </c>
@@ -8708,7 +8737,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="21"/>
     </row>
-    <row r="16" customFormat="1" ht="29" spans="2:5">
+    <row r="16" customFormat="1" ht="30" spans="2:5">
       <c r="B16" s="4" t="s">
         <v>321</v>
       </c>
@@ -8718,7 +8747,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" customFormat="1" ht="29" spans="2:4">
+    <row r="17" customFormat="1" ht="30" spans="2:4">
       <c r="B17" s="4" t="s">
         <v>322</v>
       </c>
@@ -8727,7 +8756,7 @@
       </c>
       <c r="D17" s="10"/>
     </row>
-    <row r="18" ht="58" spans="2:5">
+    <row r="18" ht="60" spans="2:5">
       <c r="B18" s="5" t="s">
         <v>324</v>
       </c>
@@ -8775,7 +8804,7 @@
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" customFormat="1" ht="29" spans="2:6">
+    <row r="22" customFormat="1" ht="30" spans="2:6">
       <c r="B22" s="4" t="s">
         <v>103</v>
       </c>
@@ -8785,7 +8814,7 @@
       <c r="D22" s="10"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" customFormat="1" ht="188.5" spans="2:6">
+    <row r="23" customFormat="1" ht="90" spans="2:6">
       <c r="B23" s="4" t="s">
         <v>105</v>
       </c>
@@ -8793,85 +8822,87 @@
         <v>335</v>
       </c>
       <c r="D23" s="10"/>
-      <c r="E23" s="13" t="s">
-        <v>107</v>
+      <c r="E23" s="22" t="s">
+        <v>336</v>
       </c>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" customFormat="1" ht="116" spans="2:6">
+    <row r="24" customFormat="1" ht="120" spans="2:6">
       <c r="B24" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" customFormat="1" ht="29" spans="2:6">
+    <row r="25" customFormat="1" ht="90" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D25" s="10"/>
-      <c r="E25" s="4"/>
+      <c r="E25" s="13" t="s">
+        <v>340</v>
+      </c>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" customFormat="1" ht="29" spans="2:6">
+    <row r="26" customFormat="1" ht="30" spans="2:6">
       <c r="B26" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" customFormat="1" ht="29" spans="2:6">
+    <row r="27" customFormat="1" ht="30" spans="2:6">
       <c r="B27" s="4" t="s">
         <v>92</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" customFormat="1" ht="29" spans="2:6">
+    <row r="28" customFormat="1" ht="30" spans="2:6">
       <c r="B28" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" customFormat="1" ht="29" spans="2:6">
+    <row r="29" customFormat="1" ht="30" spans="2:6">
       <c r="B29" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" customFormat="1" ht="29" spans="2:6">
+    <row r="30" customFormat="1" ht="30" spans="2:6">
       <c r="B30" s="4" t="s">
         <v>98</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="4"/>
@@ -8885,7 +8916,7 @@
         <v>193</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" customFormat="1" ht="46" customHeight="1" spans="2:4">
@@ -8893,7 +8924,7 @@
         <v>195</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D32" s="14"/>
     </row>
@@ -8915,13 +8946,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="33.8818181818182" customWidth="1"/>
-    <col min="3" max="3" width="46.8545454545455" customWidth="1"/>
-    <col min="4" max="4" width="57.1181818181818" customWidth="1"/>
-    <col min="5" max="5" width="54.7181818181818" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="33.8857142857143" customWidth="1"/>
+    <col min="3" max="3" width="46.8571428571429" customWidth="1"/>
+    <col min="4" max="4" width="57.1142857142857" customWidth="1"/>
+    <col min="5" max="5" width="54.7142857142857" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8945,9 +8976,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" ht="43.5" spans="1:1">
+    <row r="2" ht="45" spans="1:1">
       <c r="A2" s="20" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8956,7 +8987,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -8968,7 +8999,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8983,12 +9014,12 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" ht="29" spans="2:6">
+    <row r="6" ht="30" spans="2:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -9002,46 +9033,46 @@
         <v>57</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="8" ht="145" spans="2:5">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="8" ht="150" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" ht="70" customHeight="1" spans="2:4">
       <c r="B9" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="10" ht="29" spans="2:4">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="10" ht="30" spans="2:4">
       <c r="B10" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D10" s="10"/>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>220</v>
@@ -9049,48 +9080,48 @@
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="29" spans="2:4">
+    <row r="12" ht="30" spans="2:4">
       <c r="B12" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>358</v>
       </c>
       <c r="D12" s="10"/>
     </row>
     <row r="13" ht="38" customHeight="1" spans="2:4">
       <c r="B13" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="14" ht="29" spans="2:4">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="14" ht="30" spans="2:4">
       <c r="B14" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D14" s="10"/>
     </row>
     <row r="15" ht="153" customHeight="1" spans="2:5">
       <c r="B15" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="8" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="16" ht="58" spans="2:4">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="16" ht="75" spans="2:4">
       <c r="B16" s="5" t="s">
         <v>269</v>
       </c>
@@ -9101,7 +9132,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="17" ht="29" spans="2:3">
+    <row r="17" ht="30" spans="2:3">
       <c r="B17" s="5" t="s">
         <v>271</v>
       </c>
@@ -9109,29 +9140,29 @@
         <v>272</v>
       </c>
     </row>
-    <row r="18" ht="87" spans="2:5">
+    <row r="18" ht="90" spans="2:5">
       <c r="B18" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D18" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D19" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -9142,7 +9173,7 @@
         <v>193</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1" spans="2:4">
@@ -9150,7 +9181,7 @@
         <v>195</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D21" s="14"/>
     </row>
@@ -9169,14 +9200,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="34.5727272727273" customWidth="1"/>
-    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
-    <col min="4" max="4" width="56.5545454545455" customWidth="1"/>
-    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
-    <col min="6" max="6" width="50.2818181818182" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="34.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="56.552380952381" customWidth="1"/>
+    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="50.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -9204,7 +9235,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -9217,19 +9248,19 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="4" ht="82.5" spans="1:4">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4" ht="78" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
@@ -9244,12 +9275,12 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -9263,88 +9294,88 @@
         <v>57</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="8" ht="145" spans="2:5">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="8" ht="150" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" ht="139" customHeight="1" spans="2:5">
       <c r="B9" s="5" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="10" ht="43.5" spans="2:5">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="10" ht="45" spans="2:5">
       <c r="B10" s="5" t="s">
         <v>219</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="8" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="11" ht="203" spans="2:5">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="11" ht="210" spans="2:5">
       <c r="B11" s="5" t="s">
         <v>214</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="11" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="12" ht="203" spans="2:5">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="12" ht="210" spans="2:5">
       <c r="B12" s="5" t="s">
         <v>217</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="11" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="8" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" ht="84" customHeight="1" spans="2:5">
       <c r="B14" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>254</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E14" s="9"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>259</v>
@@ -9354,7 +9385,7 @@
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>220</v>
@@ -9362,43 +9393,43 @@
       <c r="D16" s="10"/>
       <c r="E16" s="9"/>
     </row>
-    <row r="17" ht="29" spans="2:5">
+    <row r="17" ht="30" spans="2:5">
       <c r="B17" s="5" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="8" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="18" ht="101.5" spans="2:5">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="18" ht="105" spans="2:5">
       <c r="B18" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="19" ht="29" spans="2:3">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="19" ht="30" spans="2:3">
       <c r="B19" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="20" ht="29" spans="2:3">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="20" ht="30" spans="2:3">
       <c r="B20" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C20" t="s">
         <v>220</v>
@@ -9406,38 +9437,38 @@
     </row>
     <row r="21" ht="37" customHeight="1" spans="2:5">
       <c r="B21" s="5" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" ht="72.5" spans="2:5">
+    <row r="22" ht="75" spans="2:5">
       <c r="B22" s="5" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C22" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="19" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="23" ht="43.5" spans="2:5">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="23" ht="45" spans="2:5">
       <c r="B23" s="5" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="11" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="24" ht="58" spans="2:4">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="24" ht="75" spans="2:4">
       <c r="B24" s="5" t="s">
         <v>269</v>
       </c>
@@ -9448,7 +9479,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="25" ht="29" spans="2:3">
+    <row r="25" ht="30" spans="2:3">
       <c r="B25" s="5" t="s">
         <v>271</v>
       </c>
@@ -9456,50 +9487,50 @@
         <v>272</v>
       </c>
     </row>
-    <row r="26" ht="43.5" spans="2:4">
+    <row r="26" ht="45" spans="2:4">
       <c r="B26" s="5" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C26" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="27" ht="188.5" spans="2:5">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="27" ht="210" spans="2:5">
       <c r="B27" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="28" ht="43.5" spans="2:4">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="28" ht="45" spans="2:4">
       <c r="B28" s="5" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>233</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D29" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30" spans="2:4">
@@ -9510,7 +9541,7 @@
         <v>193</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="31" ht="46" customHeight="1" spans="2:4">
@@ -9518,7 +9549,7 @@
         <v>195</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D31" s="14"/>
     </row>
@@ -9539,14 +9570,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="33.5727272727273" customWidth="1"/>
-    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
-    <col min="4" max="4" width="56.5545454545455" customWidth="1"/>
-    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
-    <col min="6" max="6" width="47.5727272727273" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="33.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="56.552380952381" customWidth="1"/>
+    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="47.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -9574,7 +9605,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -9587,7 +9618,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -9599,7 +9630,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
@@ -9614,12 +9645,12 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -9633,70 +9664,70 @@
         <v>57</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="8" ht="145" spans="2:5">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="8" ht="150" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" ht="409" customHeight="1" spans="2:5">
       <c r="B9" s="5" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="10" ht="145" spans="2:5">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="10" ht="150" spans="2:5">
       <c r="B10" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>254</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="11" ht="159.5" spans="2:5">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="11" ht="180" spans="2:5">
       <c r="B11" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C11" s="4"/>
       <c r="E11" s="11" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="12" ht="145" spans="2:5">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="12" ht="150" spans="2:5">
       <c r="B12" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C12" s="4"/>
       <c r="E12" s="11" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="13" ht="58" spans="2:4">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="13" ht="75" spans="2:4">
       <c r="B13" s="5" t="s">
         <v>269</v>
       </c>
@@ -9707,7 +9738,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="14" ht="29" spans="2:3">
+    <row r="14" ht="30" spans="2:3">
       <c r="B14" s="5" t="s">
         <v>271</v>
       </c>
@@ -9715,63 +9746,63 @@
         <v>272</v>
       </c>
     </row>
-    <row r="15" ht="43.5" spans="2:4">
+    <row r="15" ht="45" spans="2:4">
       <c r="B15" s="5" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C15" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="16" ht="188.5" spans="2:5">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="16" ht="210" spans="2:5">
       <c r="B16" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="17" ht="43.5" spans="2:4">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="17" ht="45" spans="2:4">
       <c r="B17" s="5" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>233</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D18" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="19" ht="159.5" spans="2:5">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="19" ht="165" spans="2:5">
       <c r="B19" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E19" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -9782,7 +9813,7 @@
         <v>193</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="21" ht="46" customHeight="1" spans="2:4">
@@ -9790,7 +9821,7 @@
         <v>195</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D21" s="14"/>
     </row>

--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - Medent.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - Medent.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="9"/>
+    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Medent" sheetId="11" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="448">
   <si>
     <t>Medent CCDA</t>
   </si>
@@ -632,9 +632,8 @@
       </rPr>
       <t xml:space="preserve">
 WP, DIR, PUB -&gt; work
-BA -&gt; billing
 TMP -&gt; temp
-OLD, BAD -&gt; old
+BAD -&gt; old
 All Others -&gt; home</t>
     </r>
   </si>
@@ -726,8 +725,8 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-AS, DIR, PUB, WP, WPN -&gt; work
-H, HP, HV, PRN, ORN, PRS -&gt; home
+AS, DIR, PUB, WP -&gt; work
+H, HP, HV, EC -&gt; home
 MC, PG -&gt; mobile
 TMP -&gt; temp
 BAD -&gt; old
@@ -3692,7 +3691,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-AS, DIR, PUB, WP, WPN -&gt; work
+AS, DIR, PUB, WP -&gt; work
 MC, PG -&gt; mobile
 TMP -&gt; temp
 BAD -&gt; old
@@ -3742,9 +3741,8 @@
       </rPr>
       <t xml:space="preserve">
 WP, DIR, PUB -&gt; work
-BA -&gt; billing
 TMP -&gt; temp
-OLD, BAD -&gt; old
+BAD -&gt; old
 All Others -&gt; work</t>
     </r>
   </si>
@@ -4241,6 +4239,27 @@
   </si>
   <si>
     <t>statusCode.code</t>
+  </si>
+  <si>
+    <r>
+      <t>statusCode.code -&gt; status Mapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+completed -&gt; final 
+final -&gt; final 
+aborted -&gt; entered-in-error  
+cancelled -&gt; entered-in-error  
+nullified -&gt; entered-in-error 
+All Others -&gt; unknown</t>
+    </r>
   </si>
   <si>
     <t>category</t>
@@ -5363,6 +5382,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="8"/>
       <name val="Calibri"/>
@@ -5372,15 +5400,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5537,37 +5556,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF00B050"/>
       <name val="Consolas"/>
@@ -5591,6 +5579,37 @@
       <color rgb="FF00B050"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -6112,22 +6131,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6741,7 +6760,7 @@
       <c r="A5" s="31">
         <v>3</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
@@ -6815,7 +6834,7 @@
         <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -6826,7 +6845,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="60" spans="2:7">
@@ -6838,7 +6857,7 @@
       </c>
       <c r="D4"/>
       <c r="E4" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -6858,14 +6877,14 @@
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D6"/>
       <c r="E6" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="2:6">
@@ -6873,20 +6892,20 @@
         <v>324</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" customFormat="1" ht="90" spans="2:5">
+    <row r="8" customFormat="1" ht="75" spans="2:5">
       <c r="B8" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>86</v>
@@ -6900,7 +6919,7 @@
         <v>88</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="4"/>
@@ -6910,7 +6929,7 @@
         <v>90</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="4"/>
@@ -6920,7 +6939,7 @@
         <v>92</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="4"/>
@@ -6930,7 +6949,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="4"/>
@@ -6940,7 +6959,7 @@
         <v>96</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="4"/>
@@ -6950,17 +6969,17 @@
         <v>98</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="4"/>
     </row>
     <row r="15" customFormat="1" spans="2:5">
       <c r="B15" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="4"/>
@@ -6973,7 +6992,7 @@
         <v>193</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="4"/>
@@ -6983,7 +7002,7 @@
         <v>195</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="8"/>
@@ -7153,7 +7172,7 @@
       <c r="C18" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="17" t="s">
         <v>41</v>
       </c>
     </row>
@@ -7388,7 +7407,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" ht="90" spans="2:5">
+    <row r="17" ht="75" spans="2:5">
       <c r="B17" s="4" t="s">
         <v>84</v>
       </c>
@@ -7681,7 +7700,7 @@
       <c r="D45" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="E45" s="16" t="s">
+      <c r="E45" s="17" t="s">
         <v>146</v>
       </c>
     </row>
@@ -7689,7 +7708,7 @@
       <c r="B46" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="17" t="s">
         <v>148</v>
       </c>
       <c r="D46" s="10" t="s">
@@ -7755,7 +7774,7 @@
       <c r="B52" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="17" t="s">
         <v>161</v>
       </c>
       <c r="D52" s="10" t="s">
@@ -7835,7 +7854,7 @@
       <c r="D59" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="E59" s="16" t="s">
+      <c r="E59" s="17" t="s">
         <v>176</v>
       </c>
     </row>
@@ -8339,7 +8358,7 @@
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="17" t="s">
         <v>250</v>
       </c>
       <c r="D7" t="s">
@@ -8385,7 +8404,7 @@
       <c r="B11" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="17" t="s">
         <v>261</v>
       </c>
       <c r="D11" s="12" t="s">
@@ -8477,7 +8496,7 @@
       <c r="C20" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E20" s="17"/>
+      <c r="E20" s="18"/>
     </row>
     <row r="21" ht="409.5" spans="2:5">
       <c r="B21" t="s">
@@ -8653,7 +8672,7 @@
       <c r="B8" t="s">
         <v>303</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="17" t="s">
         <v>304</v>
       </c>
       <c r="D8" s="10" t="s">
@@ -8707,7 +8726,7 @@
       <c r="B13" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="17" t="s">
         <v>315</v>
       </c>
       <c r="D13" s="10" t="s">
@@ -8760,7 +8779,7 @@
       <c r="B18" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="17" t="s">
         <v>325</v>
       </c>
       <c r="D18" s="10" t="s">
@@ -8840,7 +8859,7 @@
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" customFormat="1" ht="90" spans="2:6">
+    <row r="25" customFormat="1" ht="75" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>84</v>
       </c>
@@ -9161,7 +9180,7 @@
       <c r="D19" t="s">
         <v>376</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="18" t="s">
         <v>377</v>
       </c>
     </row>
@@ -9240,7 +9259,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="18"/>
+      <c r="F2" s="19"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1"/>
@@ -9256,7 +9275,7 @@
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="17" t="s">
         <v>381</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -9297,7 +9316,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="150" spans="2:5">
+    <row r="8" ht="105" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9307,19 +9326,19 @@
       <c r="D8" t="s">
         <v>354</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>355</v>
+      <c r="E8" s="16" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="9" ht="139" customHeight="1" spans="2:5">
       <c r="B9" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="E9" s="16" t="s">
         <v>387</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="10" ht="45" spans="2:5">
@@ -9327,11 +9346,11 @@
         <v>219</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="8" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" ht="210" spans="2:5">
@@ -9340,7 +9359,7 @@
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" ht="210" spans="2:5">
@@ -9349,16 +9368,16 @@
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" ht="84" customHeight="1" spans="2:5">
@@ -9398,11 +9417,11 @@
         <v>362</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18" ht="105" spans="2:5">
@@ -9410,13 +9429,13 @@
         <v>363</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="E18" s="16" t="s">
         <v>398</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="19" ht="30" spans="2:3">
@@ -9424,7 +9443,7 @@
         <v>366</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="20" ht="30" spans="2:3">
@@ -9437,35 +9456,35 @@
     </row>
     <row r="21" ht="37" customHeight="1" spans="2:5">
       <c r="B21" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E21" s="8"/>
     </row>
     <row r="22" ht="75" spans="2:5">
       <c r="B22" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C22" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D22" s="12"/>
-      <c r="E22" s="19" t="s">
-        <v>405</v>
+      <c r="E22" s="16" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="23" ht="45" spans="2:5">
       <c r="B23" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="24" ht="75" spans="2:4">
@@ -9489,13 +9508,13 @@
     </row>
     <row r="26" ht="45" spans="2:4">
       <c r="B26" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C26" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="27" ht="210" spans="2:5">
@@ -9506,19 +9525,19 @@
       <c r="D27" t="s">
         <v>373</v>
       </c>
-      <c r="E27" s="16" t="s">
-        <v>411</v>
+      <c r="E27" s="17" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="28" ht="45" spans="2:4">
       <c r="B28" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>233</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="29" spans="2:6">
@@ -9541,7 +9560,7 @@
         <v>193</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="31" ht="46" customHeight="1" spans="2:4">
@@ -9605,7 +9624,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -9630,7 +9649,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
@@ -9664,13 +9683,13 @@
         <v>57</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="150" spans="2:5">
+    <row r="8" ht="105" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9680,19 +9699,19 @@
       <c r="D8" t="s">
         <v>354</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>355</v>
+      <c r="E8" s="16" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="9" ht="409" customHeight="1" spans="2:5">
       <c r="B9" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" ht="150" spans="2:5">
@@ -9703,10 +9722,10 @@
         <v>254</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="E10" s="16" t="s">
         <v>421</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="11" ht="180" spans="2:5">
@@ -9715,7 +9734,7 @@
       </c>
       <c r="C11" s="4"/>
       <c r="E11" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" ht="150" spans="2:5">
@@ -9724,7 +9743,7 @@
       </c>
       <c r="C12" s="4"/>
       <c r="E12" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="13" ht="75" spans="2:4">
@@ -9748,13 +9767,13 @@
     </row>
     <row r="15" ht="45" spans="2:4">
       <c r="B15" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C15" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="16" ht="210" spans="2:5">
@@ -9765,19 +9784,19 @@
       <c r="D16" t="s">
         <v>373</v>
       </c>
-      <c r="E16" s="16" t="s">
-        <v>411</v>
+      <c r="E16" s="17" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="17" ht="45" spans="2:4">
       <c r="B17" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>233</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -9788,21 +9807,21 @@
         <v>376</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>424</v>
-      </c>
-      <c r="F18" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="F18" s="18" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="19" ht="165" spans="2:5">
       <c r="B19" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E19" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -9813,7 +9832,7 @@
         <v>193</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21" ht="46" customHeight="1" spans="2:4">

--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - Medent.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - Medent.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="7"/>
+    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="709" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Medent" sheetId="11" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="449">
   <si>
     <t>Medent CCDA</t>
   </si>
@@ -611,15 +611,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>addr.use -&gt; use Mapping</t>
     </r>
     <r>
@@ -634,7 +625,7 @@
 WP, DIR, PUB -&gt; work
 TMP -&gt; temp
 BAD -&gt; old
-All Others -&gt; home</t>
+All Others (H, HP, HV, AS, EC, MC, PG) -&gt; home</t>
     </r>
   </si>
   <si>
@@ -705,15 +696,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>telecom -&gt; use Mapping</t>
     </r>
     <r>
@@ -729,8 +711,7 @@
 H, HP, HV, EC -&gt; home
 MC, PG -&gt; mobile
 TMP -&gt; temp
-BAD -&gt; old
-All others -&gt; home</t>
+BAD -&gt; old</t>
     </r>
   </si>
   <si>
@@ -3671,15 +3652,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>telecom -&gt; use Mapping</t>
     </r>
     <r>
@@ -3695,7 +3667,7 @@
 MC, PG -&gt; mobile
 TMP -&gt; temp
 BAD -&gt; old
-All others -&gt; work</t>
+All others (H, HP, HV, EC) -&gt; work</t>
     </r>
   </si>
   <si>
@@ -3720,15 +3692,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>addr.use -&gt; use Mapping</t>
     </r>
     <r>
@@ -3743,7 +3706,7 @@
 WP, DIR, PUB -&gt; work
 TMP -&gt; temp
 BAD -&gt; old
-All Others -&gt; work</t>
+All Others (H, HP, HV, AS, EC, MC, PG) -&gt; work</t>
     </r>
   </si>
   <si>
@@ -4242,6 +4205,15 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>statusCode.code -&gt; status Mapping</t>
     </r>
     <r>
@@ -5273,6 +5245,25 @@
   </si>
   <si>
     <t>addr.use</t>
+  </si>
+  <si>
+    <r>
+      <t>addr.use -&gt; use Mapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+WP, DIR, PUB -&gt; work
+TMP -&gt; temp
+BAD -&gt; old
+All Others (H, HP, HV, AS, EC, MC, PG, BA) -&gt; work</t>
+    </r>
   </si>
   <si>
     <t>addr.streetAddressLine
@@ -5556,6 +5547,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF00B050"/>
       <name val="Consolas"/>
@@ -5581,14 +5580,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF00B050"/>
@@ -5599,7 +5590,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5607,6 +5597,7 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -6722,11 +6713,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="8.88571428571429" style="31"/>
-    <col min="2" max="2" width="35.2190476190476" customWidth="1"/>
-    <col min="3" max="3" width="92.6666666666667" customWidth="1"/>
+    <col min="1" max="1" width="8.88181818181818" style="31"/>
+    <col min="2" max="2" width="35.2181818181818" customWidth="1"/>
+    <col min="3" max="3" width="92.6636363636364" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
@@ -6799,14 +6790,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="63.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="70.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="52.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="57.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="30.8545454545455" customWidth="1"/>
+    <col min="3" max="3" width="63.4272727272727" customWidth="1"/>
+    <col min="4" max="4" width="70.7181818181818" customWidth="1"/>
+    <col min="5" max="5" width="52.4272727272727" customWidth="1"/>
+    <col min="6" max="6" width="57.5727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -6848,7 +6839,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="60" spans="2:7">
+    <row r="4" customFormat="1" ht="58" spans="2:7">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -6872,7 +6863,7 @@
       <c r="D5"/>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
@@ -6900,7 +6891,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" customFormat="1" ht="75" spans="2:5">
+    <row r="8" customFormat="1" ht="72.5" spans="2:5">
       <c r="B8" s="4" t="s">
         <v>84</v>
       </c>
@@ -6911,15 +6902,15 @@
         <v>86</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" ht="60" spans="2:5">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" ht="58" spans="2:5">
       <c r="B9" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="4"/>
@@ -6929,7 +6920,7 @@
         <v>90</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="4"/>
@@ -6939,7 +6930,7 @@
         <v>92</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="4"/>
@@ -6949,7 +6940,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="4"/>
@@ -6959,7 +6950,7 @@
         <v>96</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="4"/>
@@ -6969,17 +6960,17 @@
         <v>98</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="4"/>
     </row>
     <row r="15" customFormat="1" spans="2:5">
       <c r="B15" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="4"/>
@@ -6992,7 +6983,7 @@
         <v>193</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="4"/>
@@ -7002,7 +6993,7 @@
         <v>195</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="8"/>
@@ -7023,14 +7014,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="28.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="65.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="46.2190476190476" customWidth="1"/>
-    <col min="5" max="5" width="61.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="46.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="28.3363636363636" customWidth="1"/>
+    <col min="3" max="3" width="65.6636363636364" customWidth="1"/>
+    <col min="4" max="4" width="46.2181818181818" customWidth="1"/>
+    <col min="5" max="5" width="61.2818181818182" customWidth="1"/>
+    <col min="6" max="6" width="46.2818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -7128,7 +7119,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="30" spans="2:3">
+    <row r="10" customFormat="1" ht="29" spans="2:3">
       <c r="B10" t="s">
         <v>30</v>
       </c>
@@ -7149,7 +7140,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" ht="75" spans="2:3">
+    <row r="16" ht="72.5" spans="2:3">
       <c r="B16" t="s">
         <v>35</v>
       </c>
@@ -7165,7 +7156,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" ht="150" spans="2:5">
+    <row r="18" ht="116" spans="2:5">
       <c r="B18" t="s">
         <v>39</v>
       </c>
@@ -7176,7 +7167,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" ht="45" spans="2:5">
+    <row r="19" ht="29" spans="2:5">
       <c r="B19" s="4" t="s">
         <v>42</v>
       </c>
@@ -7185,7 +7176,7 @@
       </c>
       <c r="E19" s="10"/>
     </row>
-    <row r="20" ht="45" spans="2:5">
+    <row r="20" ht="43.5" spans="2:5">
       <c r="B20" t="s">
         <v>44</v>
       </c>
@@ -7194,13 +7185,13 @@
       </c>
       <c r="E20" s="10"/>
     </row>
-    <row r="21" ht="30" spans="2:5">
+    <row r="21" ht="29" spans="2:5">
       <c r="B21" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" ht="45" spans="2:3">
+    <row r="22" ht="43.5" spans="2:3">
       <c r="B22" s="30" t="s">
         <v>47</v>
       </c>
@@ -7224,13 +7215,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F68"/>
-  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="41.7809523809524" style="4" customWidth="1"/>
-    <col min="3" max="3" width="63.8857142857143" style="4" customWidth="1"/>
-    <col min="4" max="4" width="81.2857142857143" style="4" customWidth="1"/>
-    <col min="5" max="5" width="48.4285714285714" style="4" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="41.7818181818182" style="4" customWidth="1"/>
+    <col min="3" max="3" width="63.8818181818182" style="4" customWidth="1"/>
+    <col min="4" max="4" width="81.2818181818182" style="4" customWidth="1"/>
+    <col min="5" max="5" width="48.4272727272727" style="4" customWidth="1"/>
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7296,7 +7287,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" ht="30" spans="2:4">
+    <row r="7" ht="29" spans="2:4">
       <c r="B7" s="4" t="s">
         <v>55</v>
       </c>
@@ -7307,7 +7298,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" ht="60" spans="2:5">
+    <row r="8" ht="58" spans="2:5">
       <c r="B8" s="4" t="s">
         <v>58</v>
       </c>
@@ -7363,7 +7354,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" ht="60" spans="2:4">
+    <row r="13" ht="58" spans="2:4">
       <c r="B13" s="4" t="s">
         <v>72</v>
       </c>
@@ -7374,7 +7365,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:4">
+    <row r="14" ht="29" spans="2:4">
       <c r="B14" s="4" t="s">
         <v>75</v>
       </c>
@@ -7385,7 +7376,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" ht="30" spans="2:4">
+    <row r="15" ht="29" spans="2:4">
       <c r="B15" s="4" t="s">
         <v>78</v>
       </c>
@@ -7407,7 +7398,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" ht="75" spans="2:5">
+    <row r="17" ht="72.5" spans="2:5">
       <c r="B17" s="4" t="s">
         <v>84</v>
       </c>
@@ -7421,7 +7412,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" ht="60" spans="2:4">
+    <row r="18" ht="58" spans="2:4">
       <c r="B18" s="4" t="s">
         <v>88</v>
       </c>
@@ -7494,7 +7485,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" ht="105" spans="2:5">
+    <row r="26" ht="87" spans="2:5">
       <c r="B26" s="4" t="s">
         <v>105</v>
       </c>
@@ -7505,7 +7496,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" ht="45" spans="2:5">
+    <row r="27" ht="43.5" spans="2:5">
       <c r="B27" s="4" t="s">
         <v>108</v>
       </c>
@@ -7519,7 +7510,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28" ht="30" spans="2:5">
+    <row r="28" spans="2:5">
       <c r="B28" s="4" t="s">
         <v>112</v>
       </c>
@@ -7539,7 +7530,7 @@
       <c r="D29" s="14"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" ht="30" spans="2:5">
+    <row r="30" spans="2:5">
       <c r="B30" s="4" t="s">
         <v>116</v>
       </c>
@@ -7559,7 +7550,7 @@
       <c r="D31" s="14"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" ht="45" spans="2:5">
+    <row r="32" ht="43.5" spans="2:5">
       <c r="B32" s="4" t="s">
         <v>108</v>
       </c>
@@ -7573,7 +7564,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="33" ht="30" spans="2:4">
+    <row r="33" spans="2:4">
       <c r="B33" s="4" t="s">
         <v>112</v>
       </c>
@@ -7591,7 +7582,7 @@
       </c>
       <c r="D34" s="14"/>
     </row>
-    <row r="35" ht="30" spans="2:4">
+    <row r="35" spans="2:4">
       <c r="B35" s="4" t="s">
         <v>116</v>
       </c>
@@ -7620,7 +7611,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="38" ht="45" spans="2:5">
+    <row r="38" ht="43.5" spans="2:5">
       <c r="B38" s="4" t="s">
         <v>128</v>
       </c>
@@ -7632,7 +7623,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="39" ht="120" spans="2:6">
+    <row r="39" ht="116" spans="2:6">
       <c r="B39" s="4" t="s">
         <v>130</v>
       </c>
@@ -7643,7 +7634,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" ht="120" spans="2:6">
+    <row r="40" ht="116" spans="2:6">
       <c r="B40" s="4" t="s">
         <v>133</v>
       </c>
@@ -7690,7 +7681,7 @@
       </c>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" ht="195" spans="2:5">
+    <row r="45" ht="188.5" spans="2:5">
       <c r="B45" s="15" t="s">
         <v>143</v>
       </c>
@@ -7704,7 +7695,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="46" ht="195" spans="2:5">
+    <row r="46" ht="188.5" spans="2:5">
       <c r="B46" s="15" t="s">
         <v>147</v>
       </c>
@@ -7718,7 +7709,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" ht="195" spans="2:5">
+    <row r="47" ht="188.5" spans="2:5">
       <c r="B47" s="15" t="s">
         <v>151</v>
       </c>
@@ -7770,7 +7761,7 @@
       <c r="D51" s="10"/>
       <c r="E51" s="4"/>
     </row>
-    <row r="52" ht="150" spans="2:5">
+    <row r="52" ht="145" spans="2:5">
       <c r="B52" s="10" t="s">
         <v>160</v>
       </c>
@@ -7844,7 +7835,7 @@
       <c r="D58" s="10"/>
       <c r="E58" s="8"/>
     </row>
-    <row r="59" ht="180" spans="2:5">
+    <row r="59" ht="174" spans="2:5">
       <c r="B59" s="10" t="s">
         <v>174</v>
       </c>
@@ -7858,7 +7849,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" ht="255" spans="2:6">
+    <row r="60" ht="246.5" spans="2:6">
       <c r="B60" s="4" t="s">
         <v>177</v>
       </c>
@@ -7889,7 +7880,7 @@
       <c r="D62" s="10"/>
       <c r="F62" s="4"/>
     </row>
-    <row r="63" ht="210" spans="2:6">
+    <row r="63" ht="203" spans="2:6">
       <c r="B63" s="4" t="s">
         <v>184</v>
       </c>
@@ -7967,14 +7958,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="63.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="70.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="52.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="57.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="30.8545454545455" customWidth="1"/>
+    <col min="3" max="3" width="63.4272727272727" customWidth="1"/>
+    <col min="4" max="4" width="70.7181818181818" customWidth="1"/>
+    <col min="5" max="5" width="52.4272727272727" customWidth="1"/>
+    <col min="6" max="6" width="57.5727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8016,7 +8007,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" ht="60" spans="2:7">
+    <row r="4" ht="58" spans="2:7">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -8047,7 +8038,7 @@
       </c>
       <c r="E6" s="25"/>
     </row>
-    <row r="7" ht="120" spans="2:6">
+    <row r="7" ht="116" spans="2:6">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
@@ -8100,7 +8091,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="11" ht="225" spans="2:5">
+    <row r="11" ht="203" spans="2:5">
       <c r="B11" s="5" t="s">
         <v>214</v>
       </c>
@@ -8136,7 +8127,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:5">
+    <row r="14" ht="29" spans="2:5">
       <c r="B14" s="5" t="s">
         <v>221</v>
       </c>
@@ -8150,7 +8141,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="15" ht="120" spans="2:5">
+    <row r="15" ht="101.5" spans="2:5">
       <c r="B15" s="5" t="s">
         <v>225</v>
       </c>
@@ -8164,7 +8155,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="16" ht="45" spans="2:5">
+    <row r="16" ht="43.5" spans="2:5">
       <c r="B16" s="5" t="s">
         <v>229</v>
       </c>
@@ -8176,7 +8167,7 @@
       </c>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" ht="45" spans="2:5">
+    <row r="17" ht="43.5" spans="2:5">
       <c r="B17" s="5" t="s">
         <v>232</v>
       </c>
@@ -8188,7 +8179,7 @@
       </c>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" ht="45" spans="2:5">
+    <row r="18" ht="43.5" spans="2:5">
       <c r="B18" t="s">
         <v>235</v>
       </c>
@@ -8202,7 +8193,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="19" ht="60" spans="2:5">
+    <row r="19" ht="58" spans="2:5">
       <c r="B19" s="5" t="s">
         <v>238</v>
       </c>
@@ -8267,14 +8258,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="35.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="42.2857142857143" style="4" customWidth="1"/>
-    <col min="4" max="4" width="73.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="35.1454545454545" customWidth="1"/>
+    <col min="3" max="3" width="42.2818181818182" style="4" customWidth="1"/>
+    <col min="4" max="4" width="73.5727272727273" customWidth="1"/>
     <col min="5" max="5" width="53" customWidth="1"/>
-    <col min="6" max="6" width="51.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="51.7181818181818" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8316,7 +8307,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="4" ht="60" spans="1:5">
+    <row r="4" ht="58" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -8343,7 +8334,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
@@ -8354,7 +8345,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" ht="165" spans="2:5">
+    <row r="7" ht="159.5" spans="2:5">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
@@ -8380,7 +8371,7 @@
       </c>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" ht="30" spans="2:5">
+    <row r="9" ht="29" spans="2:5">
       <c r="B9" s="5" t="s">
         <v>256</v>
       </c>
@@ -8400,7 +8391,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" ht="30" spans="2:4">
+    <row r="11" ht="29" spans="2:4">
       <c r="B11" s="5" t="s">
         <v>260</v>
       </c>
@@ -8411,7 +8402,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="12" ht="60" spans="2:5">
+    <row r="12" ht="58" spans="2:5">
       <c r="B12" s="5" t="s">
         <v>263</v>
       </c>
@@ -8437,7 +8428,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="60" spans="2:4">
+    <row r="15" customFormat="1" ht="58" spans="2:4">
       <c r="B15" s="5" t="s">
         <v>269</v>
       </c>
@@ -8448,7 +8439,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="30" spans="2:3">
+    <row r="16" customFormat="1" ht="29" spans="2:3">
       <c r="B16" s="5" t="s">
         <v>271</v>
       </c>
@@ -8456,7 +8447,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="17" ht="60" spans="2:4">
+    <row r="17" ht="58" spans="2:4">
       <c r="B17" t="s">
         <v>273</v>
       </c>
@@ -8475,7 +8466,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="19" ht="45" spans="2:5">
+    <row r="19" ht="43.5" spans="2:5">
       <c r="B19" t="s">
         <v>278</v>
       </c>
@@ -8509,7 +8500,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="22" ht="60" spans="2:5">
+    <row r="22" ht="58" spans="2:5">
       <c r="B22" t="s">
         <v>287</v>
       </c>
@@ -8578,14 +8569,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="27.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="50.8857142857143" customWidth="1"/>
-    <col min="4" max="4" width="72.8571428571429" customWidth="1"/>
-    <col min="5" max="5" width="46.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="45.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="27.3363636363636" customWidth="1"/>
+    <col min="3" max="3" width="50.8818181818182" customWidth="1"/>
+    <col min="4" max="4" width="72.8545454545455" customWidth="1"/>
+    <col min="5" max="5" width="46.4272727272727" customWidth="1"/>
+    <col min="6" max="6" width="45.7181818181818" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8643,7 +8634,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
@@ -8692,7 +8683,7 @@
       <c r="D9" s="10"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" ht="30" spans="2:5">
+    <row r="10" ht="29" spans="2:5">
       <c r="B10" s="4" t="s">
         <v>309</v>
       </c>
@@ -8702,7 +8693,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" ht="30" spans="2:5">
+    <row r="11" ht="29" spans="2:5">
       <c r="B11" s="4" t="s">
         <v>311</v>
       </c>
@@ -8712,7 +8703,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="30" spans="2:5">
+    <row r="12" ht="29" spans="2:5">
       <c r="B12" s="4" t="s">
         <v>312</v>
       </c>
@@ -8746,7 +8737,7 @@
       <c r="D14" s="10"/>
       <c r="E14" s="21"/>
     </row>
-    <row r="15" customFormat="1" ht="30" spans="2:5">
+    <row r="15" customFormat="1" ht="29" spans="2:5">
       <c r="B15" s="4" t="s">
         <v>319</v>
       </c>
@@ -8756,7 +8747,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="21"/>
     </row>
-    <row r="16" customFormat="1" ht="30" spans="2:5">
+    <row r="16" customFormat="1" ht="29" spans="2:5">
       <c r="B16" s="4" t="s">
         <v>321</v>
       </c>
@@ -8766,7 +8757,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" customFormat="1" ht="30" spans="2:4">
+    <row r="17" customFormat="1" ht="29" spans="2:4">
       <c r="B17" s="4" t="s">
         <v>322</v>
       </c>
@@ -8775,7 +8766,7 @@
       </c>
       <c r="D17" s="10"/>
     </row>
-    <row r="18" ht="60" spans="2:5">
+    <row r="18" ht="58" spans="2:5">
       <c r="B18" s="5" t="s">
         <v>324</v>
       </c>
@@ -8823,7 +8814,7 @@
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" customFormat="1" ht="30" spans="2:6">
+    <row r="22" customFormat="1" ht="29" spans="2:6">
       <c r="B22" s="4" t="s">
         <v>103</v>
       </c>
@@ -8833,7 +8824,7 @@
       <c r="D22" s="10"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" customFormat="1" ht="90" spans="2:6">
+    <row r="23" customFormat="1" ht="87" spans="2:6">
       <c r="B23" s="4" t="s">
         <v>105</v>
       </c>
@@ -8846,7 +8837,7 @@
       </c>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" customFormat="1" ht="120" spans="2:6">
+    <row r="24" customFormat="1" ht="116" spans="2:6">
       <c r="B24" s="4" t="s">
         <v>88</v>
       </c>
@@ -8859,7 +8850,7 @@
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" customFormat="1" ht="75" spans="2:6">
+    <row r="25" customFormat="1" ht="72.5" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>84</v>
       </c>
@@ -8872,7 +8863,7 @@
       </c>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" customFormat="1" ht="30" spans="2:6">
+    <row r="26" customFormat="1" ht="29" spans="2:6">
       <c r="B26" s="4" t="s">
         <v>90</v>
       </c>
@@ -8883,7 +8874,7 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" customFormat="1" ht="30" spans="2:6">
+    <row r="27" customFormat="1" ht="29" spans="2:6">
       <c r="B27" s="4" t="s">
         <v>92</v>
       </c>
@@ -8894,7 +8885,7 @@
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" customFormat="1" ht="30" spans="2:6">
+    <row r="28" customFormat="1" ht="29" spans="2:6">
       <c r="B28" s="4" t="s">
         <v>94</v>
       </c>
@@ -8905,7 +8896,7 @@
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" customFormat="1" ht="30" spans="2:6">
+    <row r="29" customFormat="1" ht="29" spans="2:6">
       <c r="B29" s="4" t="s">
         <v>96</v>
       </c>
@@ -8916,7 +8907,7 @@
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" customFormat="1" ht="30" spans="2:6">
+    <row r="30" customFormat="1" ht="29" spans="2:6">
       <c r="B30" s="4" t="s">
         <v>98</v>
       </c>
@@ -8965,13 +8956,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="33.8857142857143" customWidth="1"/>
-    <col min="3" max="3" width="46.8571428571429" customWidth="1"/>
-    <col min="4" max="4" width="57.1142857142857" customWidth="1"/>
-    <col min="5" max="5" width="54.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="33.8818181818182" customWidth="1"/>
+    <col min="3" max="3" width="46.8545454545455" customWidth="1"/>
+    <col min="4" max="4" width="57.1181818181818" customWidth="1"/>
+    <col min="5" max="5" width="54.7181818181818" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8995,7 +8986,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" ht="45" spans="1:1">
+    <row r="2" ht="43.5" spans="1:1">
       <c r="A2" s="20" t="s">
         <v>348</v>
       </c>
@@ -9033,7 +9024,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" ht="30" spans="2:6">
+    <row r="6" ht="29" spans="2:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
@@ -9055,7 +9046,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="150" spans="2:5">
+    <row r="8" ht="145" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9080,7 +9071,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="10" ht="30" spans="2:4">
+    <row r="10" ht="29" spans="2:4">
       <c r="B10" s="5" t="s">
         <v>359</v>
       </c>
@@ -9099,7 +9090,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="30" spans="2:4">
+    <row r="12" ht="29" spans="2:4">
       <c r="B12" s="5" t="s">
         <v>362</v>
       </c>
@@ -9119,7 +9110,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:4">
+    <row r="14" ht="29" spans="2:4">
       <c r="B14" s="4" t="s">
         <v>366</v>
       </c>
@@ -9140,7 +9131,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="16" ht="75" spans="2:4">
+    <row r="16" ht="58" spans="2:4">
       <c r="B16" s="5" t="s">
         <v>269</v>
       </c>
@@ -9151,7 +9142,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="17" ht="30" spans="2:3">
+    <row r="17" ht="29" spans="2:3">
       <c r="B17" s="5" t="s">
         <v>271</v>
       </c>
@@ -9159,7 +9150,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="18" ht="90" spans="2:5">
+    <row r="18" ht="87" spans="2:5">
       <c r="B18" t="s">
         <v>371</v>
       </c>
@@ -9219,14 +9210,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="34.5714285714286" customWidth="1"/>
-    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="56.552380952381" customWidth="1"/>
-    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="50.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="34.5727272727273" customWidth="1"/>
+    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
+    <col min="4" max="4" width="56.5545454545455" customWidth="1"/>
+    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
+    <col min="6" max="6" width="50.2818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -9270,7 +9261,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" ht="78" spans="1:4">
+    <row r="4" ht="82.5" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -9294,7 +9285,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
@@ -9316,7 +9307,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="105" spans="2:5">
+    <row r="8" ht="101.5" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9341,7 +9332,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="10" ht="45" spans="2:5">
+    <row r="10" ht="43.5" spans="2:5">
       <c r="B10" s="5" t="s">
         <v>219</v>
       </c>
@@ -9353,7 +9344,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="11" ht="210" spans="2:5">
+    <row r="11" ht="203" spans="2:5">
       <c r="B11" s="5" t="s">
         <v>214</v>
       </c>
@@ -9362,7 +9353,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="12" ht="210" spans="2:5">
+    <row r="12" ht="203" spans="2:5">
       <c r="B12" s="5" t="s">
         <v>217</v>
       </c>
@@ -9412,7 +9403,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="9"/>
     </row>
-    <row r="17" ht="30" spans="2:5">
+    <row r="17" ht="29" spans="2:5">
       <c r="B17" s="5" t="s">
         <v>362</v>
       </c>
@@ -9424,7 +9415,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="18" ht="105" spans="2:5">
+    <row r="18" ht="101.5" spans="2:5">
       <c r="B18" s="4" t="s">
         <v>363</v>
       </c>
@@ -9438,7 +9429,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="19" ht="30" spans="2:3">
+    <row r="19" ht="29" spans="2:3">
       <c r="B19" s="4" t="s">
         <v>366</v>
       </c>
@@ -9446,7 +9437,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="20" ht="30" spans="2:3">
+    <row r="20" ht="29" spans="2:3">
       <c r="B20" s="4" t="s">
         <v>368</v>
       </c>
@@ -9466,7 +9457,7 @@
       </c>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" ht="75" spans="2:5">
+    <row r="22" ht="72.5" spans="2:5">
       <c r="B22" s="5" t="s">
         <v>404</v>
       </c>
@@ -9478,7 +9469,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="23" ht="45" spans="2:5">
+    <row r="23" ht="43.5" spans="2:5">
       <c r="B23" s="5" t="s">
         <v>407</v>
       </c>
@@ -9487,7 +9478,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="24" ht="75" spans="2:4">
+    <row r="24" ht="58" spans="2:4">
       <c r="B24" s="5" t="s">
         <v>269</v>
       </c>
@@ -9498,7 +9489,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="25" ht="30" spans="2:3">
+    <row r="25" ht="29" spans="2:3">
       <c r="B25" s="5" t="s">
         <v>271</v>
       </c>
@@ -9506,7 +9497,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="26" ht="45" spans="2:4">
+    <row r="26" ht="43.5" spans="2:4">
       <c r="B26" s="5" t="s">
         <v>409</v>
       </c>
@@ -9517,7 +9508,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="27" ht="210" spans="2:5">
+    <row r="27" ht="188.5" spans="2:5">
       <c r="B27" s="5" t="s">
         <v>371</v>
       </c>
@@ -9529,7 +9520,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="28" ht="45" spans="2:4">
+    <row r="28" ht="43.5" spans="2:4">
       <c r="B28" s="5" t="s">
         <v>413</v>
       </c>
@@ -9589,14 +9580,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="33.5714285714286" customWidth="1"/>
-    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="56.552380952381" customWidth="1"/>
-    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="47.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="33.5727272727273" customWidth="1"/>
+    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
+    <col min="4" max="4" width="56.5545454545455" customWidth="1"/>
+    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
+    <col min="6" max="6" width="47.5727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -9664,7 +9655,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
@@ -9689,7 +9680,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="105" spans="2:5">
+    <row r="8" ht="101.5" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9714,7 +9705,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="10" ht="150" spans="2:5">
+    <row r="10" ht="145" spans="2:5">
       <c r="B10" s="5" t="s">
         <v>356</v>
       </c>
@@ -9728,7 +9719,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="11" ht="180" spans="2:5">
+    <row r="11" ht="159.5" spans="2:5">
       <c r="B11" s="5" t="s">
         <v>359</v>
       </c>
@@ -9737,7 +9728,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="12" ht="150" spans="2:5">
+    <row r="12" ht="145" spans="2:5">
       <c r="B12" s="5" t="s">
         <v>361</v>
       </c>
@@ -9746,7 +9737,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="13" ht="75" spans="2:4">
+    <row r="13" ht="58" spans="2:4">
       <c r="B13" s="5" t="s">
         <v>269</v>
       </c>
@@ -9757,7 +9748,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:3">
+    <row r="14" ht="29" spans="2:3">
       <c r="B14" s="5" t="s">
         <v>271</v>
       </c>
@@ -9765,7 +9756,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="15" ht="45" spans="2:4">
+    <row r="15" ht="43.5" spans="2:4">
       <c r="B15" s="5" t="s">
         <v>409</v>
       </c>
@@ -9776,7 +9767,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="16" ht="210" spans="2:5">
+    <row r="16" ht="188.5" spans="2:5">
       <c r="B16" s="5" t="s">
         <v>371</v>
       </c>
@@ -9788,7 +9779,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="17" ht="45" spans="2:4">
+    <row r="17" ht="43.5" spans="2:4">
       <c r="B17" s="5" t="s">
         <v>413</v>
       </c>
@@ -9813,7 +9804,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="19" ht="165" spans="2:5">
+    <row r="19" ht="159.5" spans="2:5">
       <c r="B19" t="s">
         <v>426</v>
       </c>

--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - Medent.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - Medent.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="709" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Medent" sheetId="11" r:id="rId1"/>
@@ -611,6 +611,15 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>addr.use -&gt; use Mapping</t>
     </r>
     <r>
@@ -678,9 +687,37 @@
       }],</t>
   </si>
   <si>
-    <t>If telecom.value contains "tel:" then "phone".
-If telecom.value contains "mailto:" then "email".
-Otherwise "other"</t>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>telecom.value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> contains 
+  "tel:" then "phone",
+  "mailto:" then "email",
+  "fax:" then "fax",
+  "pager:" then "pager",
+  "sms:" then "sms",
+  "http://" or "https://" or "www." then "url",
+  All Others "other".</t>
+    </r>
   </si>
   <si>
     <t>telecom -&gt; value</t>
@@ -696,6 +733,15 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>telecom -&gt; use Mapping</t>
     </r>
     <r>
@@ -3652,6 +3698,15 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>telecom -&gt; use Mapping</t>
     </r>
     <r>
@@ -3692,6 +3747,15 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>addr.use -&gt; use Mapping</t>
     </r>
     <r>
@@ -5248,6 +5312,15 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>addr.use -&gt; use Mapping</t>
     </r>
     <r>
@@ -5548,7 +5621,30 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5578,29 +5674,6 @@
       <color rgb="FF00B050"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -6713,11 +6786,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="8.88181818181818" style="31"/>
-    <col min="2" max="2" width="35.2181818181818" customWidth="1"/>
-    <col min="3" max="3" width="92.6636363636364" customWidth="1"/>
+    <col min="1" max="1" width="8.88571428571429" style="31"/>
+    <col min="2" max="2" width="35.2190476190476" customWidth="1"/>
+    <col min="3" max="3" width="92.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
@@ -6790,14 +6863,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="30.8545454545455" customWidth="1"/>
-    <col min="3" max="3" width="63.4272727272727" customWidth="1"/>
-    <col min="4" max="4" width="70.7181818181818" customWidth="1"/>
-    <col min="5" max="5" width="52.4272727272727" customWidth="1"/>
-    <col min="6" max="6" width="57.5727272727273" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="63.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="70.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="52.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="57.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -6839,7 +6912,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="58" spans="2:7">
+    <row r="4" customFormat="1" ht="60" spans="2:7">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -6863,7 +6936,7 @@
       <c r="D5"/>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
@@ -6891,7 +6964,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" customFormat="1" ht="72.5" spans="2:5">
+    <row r="8" customFormat="1" ht="75" spans="2:5">
       <c r="B8" s="4" t="s">
         <v>84</v>
       </c>
@@ -6905,7 +6978,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="9" customFormat="1" ht="58" spans="2:5">
+    <row r="9" customFormat="1" ht="60" spans="2:5">
       <c r="B9" s="4" t="s">
         <v>88</v>
       </c>
@@ -7014,14 +7087,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="28.3363636363636" customWidth="1"/>
-    <col min="3" max="3" width="65.6636363636364" customWidth="1"/>
-    <col min="4" max="4" width="46.2181818181818" customWidth="1"/>
-    <col min="5" max="5" width="61.2818181818182" customWidth="1"/>
-    <col min="6" max="6" width="46.2818181818182" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="28.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="65.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="46.2190476190476" customWidth="1"/>
+    <col min="5" max="5" width="61.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="46.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -7119,7 +7192,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="29" spans="2:3">
+    <row r="10" customFormat="1" ht="30" spans="2:3">
       <c r="B10" t="s">
         <v>30</v>
       </c>
@@ -7140,7 +7213,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" ht="72.5" spans="2:3">
+    <row r="16" ht="75" spans="2:3">
       <c r="B16" t="s">
         <v>35</v>
       </c>
@@ -7156,7 +7229,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" ht="116" spans="2:5">
+    <row r="18" ht="150" spans="2:5">
       <c r="B18" t="s">
         <v>39</v>
       </c>
@@ -7167,7 +7240,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" ht="29" spans="2:5">
+    <row r="19" ht="45" spans="2:5">
       <c r="B19" s="4" t="s">
         <v>42</v>
       </c>
@@ -7176,7 +7249,7 @@
       </c>
       <c r="E19" s="10"/>
     </row>
-    <row r="20" ht="43.5" spans="2:5">
+    <row r="20" ht="45" spans="2:5">
       <c r="B20" t="s">
         <v>44</v>
       </c>
@@ -7185,13 +7258,13 @@
       </c>
       <c r="E20" s="10"/>
     </row>
-    <row r="21" ht="29" spans="2:5">
+    <row r="21" ht="30" spans="2:5">
       <c r="B21" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" ht="43.5" spans="2:3">
+    <row r="22" ht="45" spans="2:3">
       <c r="B22" s="30" t="s">
         <v>47</v>
       </c>
@@ -7215,13 +7288,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F68"/>
-  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="41.7818181818182" style="4" customWidth="1"/>
-    <col min="3" max="3" width="63.8818181818182" style="4" customWidth="1"/>
-    <col min="4" max="4" width="81.2818181818182" style="4" customWidth="1"/>
-    <col min="5" max="5" width="48.4272727272727" style="4" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="41.7809523809524" style="4" customWidth="1"/>
+    <col min="3" max="3" width="63.8857142857143" style="4" customWidth="1"/>
+    <col min="4" max="4" width="81.2857142857143" style="4" customWidth="1"/>
+    <col min="5" max="5" width="48.4285714285714" style="4" customWidth="1"/>
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7287,7 +7360,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" ht="29" spans="2:4">
+    <row r="7" ht="30" spans="2:4">
       <c r="B7" s="4" t="s">
         <v>55</v>
       </c>
@@ -7298,7 +7371,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" ht="58" spans="2:5">
+    <row r="8" ht="60" spans="2:5">
       <c r="B8" s="4" t="s">
         <v>58</v>
       </c>
@@ -7354,7 +7427,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" ht="58" spans="2:4">
+    <row r="13" ht="60" spans="2:4">
       <c r="B13" s="4" t="s">
         <v>72</v>
       </c>
@@ -7365,7 +7438,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" ht="29" spans="2:4">
+    <row r="14" ht="30" spans="2:4">
       <c r="B14" s="4" t="s">
         <v>75</v>
       </c>
@@ -7376,7 +7449,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" ht="29" spans="2:4">
+    <row r="15" ht="30" spans="2:4">
       <c r="B15" s="4" t="s">
         <v>78</v>
       </c>
@@ -7398,7 +7471,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" ht="72.5" spans="2:5">
+    <row r="17" ht="75" spans="2:5">
       <c r="B17" s="4" t="s">
         <v>84</v>
       </c>
@@ -7412,7 +7485,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" ht="58" spans="2:4">
+    <row r="18" ht="60" spans="2:4">
       <c r="B18" s="4" t="s">
         <v>88</v>
       </c>
@@ -7466,14 +7539,14 @@
       </c>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" ht="48" customHeight="1" spans="2:5">
+    <row r="24" ht="120" spans="2:5">
       <c r="B24" s="4" t="s">
         <v>100</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="17" t="s">
         <v>102</v>
       </c>
     </row>
@@ -7485,7 +7558,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" ht="87" spans="2:5">
+    <row r="26" ht="90" spans="2:5">
       <c r="B26" s="4" t="s">
         <v>105</v>
       </c>
@@ -7496,7 +7569,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" ht="43.5" spans="2:5">
+    <row r="27" ht="45" spans="2:5">
       <c r="B27" s="4" t="s">
         <v>108</v>
       </c>
@@ -7510,7 +7583,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="2:5">
+    <row r="28" ht="30" spans="2:5">
       <c r="B28" s="4" t="s">
         <v>112</v>
       </c>
@@ -7530,7 +7603,7 @@
       <c r="D29" s="14"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" spans="2:5">
+    <row r="30" ht="30" spans="2:5">
       <c r="B30" s="4" t="s">
         <v>116</v>
       </c>
@@ -7550,7 +7623,7 @@
       <c r="D31" s="14"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" ht="43.5" spans="2:5">
+    <row r="32" ht="45" spans="2:5">
       <c r="B32" s="4" t="s">
         <v>108</v>
       </c>
@@ -7564,7 +7637,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="2:4">
+    <row r="33" ht="30" spans="2:4">
       <c r="B33" s="4" t="s">
         <v>112</v>
       </c>
@@ -7582,7 +7655,7 @@
       </c>
       <c r="D34" s="14"/>
     </row>
-    <row r="35" spans="2:4">
+    <row r="35" ht="30" spans="2:4">
       <c r="B35" s="4" t="s">
         <v>116</v>
       </c>
@@ -7611,7 +7684,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="38" ht="43.5" spans="2:5">
+    <row r="38" ht="45" spans="2:5">
       <c r="B38" s="4" t="s">
         <v>128</v>
       </c>
@@ -7623,7 +7696,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="39" ht="116" spans="2:6">
+    <row r="39" ht="120" spans="2:6">
       <c r="B39" s="4" t="s">
         <v>130</v>
       </c>
@@ -7634,7 +7707,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" ht="116" spans="2:6">
+    <row r="40" ht="120" spans="2:6">
       <c r="B40" s="4" t="s">
         <v>133</v>
       </c>
@@ -7681,7 +7754,7 @@
       </c>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" ht="188.5" spans="2:5">
+    <row r="45" ht="195" spans="2:5">
       <c r="B45" s="15" t="s">
         <v>143</v>
       </c>
@@ -7695,7 +7768,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="46" ht="188.5" spans="2:5">
+    <row r="46" ht="195" spans="2:5">
       <c r="B46" s="15" t="s">
         <v>147</v>
       </c>
@@ -7709,7 +7782,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" ht="188.5" spans="2:5">
+    <row r="47" ht="195" spans="2:5">
       <c r="B47" s="15" t="s">
         <v>151</v>
       </c>
@@ -7761,7 +7834,7 @@
       <c r="D51" s="10"/>
       <c r="E51" s="4"/>
     </row>
-    <row r="52" ht="145" spans="2:5">
+    <row r="52" ht="150" spans="2:5">
       <c r="B52" s="10" t="s">
         <v>160</v>
       </c>
@@ -7835,7 +7908,7 @@
       <c r="D58" s="10"/>
       <c r="E58" s="8"/>
     </row>
-    <row r="59" ht="174" spans="2:5">
+    <row r="59" ht="180" spans="2:5">
       <c r="B59" s="10" t="s">
         <v>174</v>
       </c>
@@ -7849,7 +7922,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" ht="246.5" spans="2:6">
+    <row r="60" ht="255" spans="2:6">
       <c r="B60" s="4" t="s">
         <v>177</v>
       </c>
@@ -7880,7 +7953,7 @@
       <c r="D62" s="10"/>
       <c r="F62" s="4"/>
     </row>
-    <row r="63" ht="203" spans="2:6">
+    <row r="63" ht="210" spans="2:6">
       <c r="B63" s="4" t="s">
         <v>184</v>
       </c>
@@ -7958,14 +8031,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="30.8545454545455" customWidth="1"/>
-    <col min="3" max="3" width="63.4272727272727" customWidth="1"/>
-    <col min="4" max="4" width="70.7181818181818" customWidth="1"/>
-    <col min="5" max="5" width="52.4272727272727" customWidth="1"/>
-    <col min="6" max="6" width="57.5727272727273" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="63.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="70.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="52.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="57.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8007,7 +8080,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" ht="58" spans="2:7">
+    <row r="4" ht="60" spans="2:7">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -8038,7 +8111,7 @@
       </c>
       <c r="E6" s="25"/>
     </row>
-    <row r="7" ht="116" spans="2:6">
+    <row r="7" ht="120" spans="2:6">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
@@ -8091,7 +8164,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="11" ht="203" spans="2:5">
+    <row r="11" ht="225" spans="2:5">
       <c r="B11" s="5" t="s">
         <v>214</v>
       </c>
@@ -8127,7 +8200,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" ht="29" spans="2:5">
+    <row r="14" ht="30" spans="2:5">
       <c r="B14" s="5" t="s">
         <v>221</v>
       </c>
@@ -8141,7 +8214,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="15" ht="101.5" spans="2:5">
+    <row r="15" ht="120" spans="2:5">
       <c r="B15" s="5" t="s">
         <v>225</v>
       </c>
@@ -8155,7 +8228,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="16" ht="43.5" spans="2:5">
+    <row r="16" ht="45" spans="2:5">
       <c r="B16" s="5" t="s">
         <v>229</v>
       </c>
@@ -8167,7 +8240,7 @@
       </c>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" ht="43.5" spans="2:5">
+    <row r="17" ht="45" spans="2:5">
       <c r="B17" s="5" t="s">
         <v>232</v>
       </c>
@@ -8179,7 +8252,7 @@
       </c>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" ht="43.5" spans="2:5">
+    <row r="18" ht="45" spans="2:5">
       <c r="B18" t="s">
         <v>235</v>
       </c>
@@ -8193,7 +8266,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="19" ht="58" spans="2:5">
+    <row r="19" ht="60" spans="2:5">
       <c r="B19" s="5" t="s">
         <v>238</v>
       </c>
@@ -8258,14 +8331,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="35.1454545454545" customWidth="1"/>
-    <col min="3" max="3" width="42.2818181818182" style="4" customWidth="1"/>
-    <col min="4" max="4" width="73.5727272727273" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="35.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="42.2857142857143" style="4" customWidth="1"/>
+    <col min="4" max="4" width="73.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="53" customWidth="1"/>
-    <col min="6" max="6" width="51.7181818181818" customWidth="1"/>
+    <col min="6" max="6" width="51.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8307,7 +8380,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="4" ht="58" spans="1:5">
+    <row r="4" ht="60" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -8334,7 +8407,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
@@ -8345,7 +8418,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" ht="159.5" spans="2:5">
+    <row r="7" ht="165" spans="2:5">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
@@ -8371,7 +8444,7 @@
       </c>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" ht="29" spans="2:5">
+    <row r="9" ht="30" spans="2:5">
       <c r="B9" s="5" t="s">
         <v>256</v>
       </c>
@@ -8391,7 +8464,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" ht="29" spans="2:4">
+    <row r="11" ht="30" spans="2:4">
       <c r="B11" s="5" t="s">
         <v>260</v>
       </c>
@@ -8402,7 +8475,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="12" ht="58" spans="2:5">
+    <row r="12" ht="60" spans="2:5">
       <c r="B12" s="5" t="s">
         <v>263</v>
       </c>
@@ -8428,7 +8501,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="58" spans="2:4">
+    <row r="15" customFormat="1" ht="60" spans="2:4">
       <c r="B15" s="5" t="s">
         <v>269</v>
       </c>
@@ -8439,7 +8512,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="29" spans="2:3">
+    <row r="16" customFormat="1" ht="30" spans="2:3">
       <c r="B16" s="5" t="s">
         <v>271</v>
       </c>
@@ -8447,7 +8520,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="17" ht="58" spans="2:4">
+    <row r="17" ht="60" spans="2:4">
       <c r="B17" t="s">
         <v>273</v>
       </c>
@@ -8466,7 +8539,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="19" ht="43.5" spans="2:5">
+    <row r="19" ht="45" spans="2:5">
       <c r="B19" t="s">
         <v>278</v>
       </c>
@@ -8500,7 +8573,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="22" ht="58" spans="2:5">
+    <row r="22" ht="60" spans="2:5">
       <c r="B22" t="s">
         <v>287</v>
       </c>
@@ -8569,14 +8642,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="27.3363636363636" customWidth="1"/>
-    <col min="3" max="3" width="50.8818181818182" customWidth="1"/>
-    <col min="4" max="4" width="72.8545454545455" customWidth="1"/>
-    <col min="5" max="5" width="46.4272727272727" customWidth="1"/>
-    <col min="6" max="6" width="45.7181818181818" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="27.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="50.8857142857143" customWidth="1"/>
+    <col min="4" max="4" width="72.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="46.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="45.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8634,7 +8707,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
@@ -8683,7 +8756,7 @@
       <c r="D9" s="10"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" ht="29" spans="2:5">
+    <row r="10" ht="30" spans="2:5">
       <c r="B10" s="4" t="s">
         <v>309</v>
       </c>
@@ -8693,7 +8766,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" ht="29" spans="2:5">
+    <row r="11" ht="30" spans="2:5">
       <c r="B11" s="4" t="s">
         <v>311</v>
       </c>
@@ -8703,7 +8776,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="29" spans="2:5">
+    <row r="12" ht="30" spans="2:5">
       <c r="B12" s="4" t="s">
         <v>312</v>
       </c>
@@ -8737,7 +8810,7 @@
       <c r="D14" s="10"/>
       <c r="E14" s="21"/>
     </row>
-    <row r="15" customFormat="1" ht="29" spans="2:5">
+    <row r="15" customFormat="1" ht="30" spans="2:5">
       <c r="B15" s="4" t="s">
         <v>319</v>
       </c>
@@ -8747,7 +8820,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="21"/>
     </row>
-    <row r="16" customFormat="1" ht="29" spans="2:5">
+    <row r="16" customFormat="1" ht="30" spans="2:5">
       <c r="B16" s="4" t="s">
         <v>321</v>
       </c>
@@ -8757,7 +8830,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" customFormat="1" ht="29" spans="2:4">
+    <row r="17" customFormat="1" ht="30" spans="2:4">
       <c r="B17" s="4" t="s">
         <v>322</v>
       </c>
@@ -8766,7 +8839,7 @@
       </c>
       <c r="D17" s="10"/>
     </row>
-    <row r="18" ht="58" spans="2:5">
+    <row r="18" ht="60" spans="2:5">
       <c r="B18" s="5" t="s">
         <v>324</v>
       </c>
@@ -8801,7 +8874,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="21" customFormat="1" ht="50" customHeight="1" spans="2:6">
+    <row r="21" customFormat="1" ht="120" spans="2:6">
       <c r="B21" s="4" t="s">
         <v>100</v>
       </c>
@@ -8809,12 +8882,12 @@
       <c r="D21" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="17" t="s">
         <v>102</v>
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" customFormat="1" ht="29" spans="2:6">
+    <row r="22" customFormat="1" ht="30" spans="2:6">
       <c r="B22" s="4" t="s">
         <v>103</v>
       </c>
@@ -8824,7 +8897,7 @@
       <c r="D22" s="10"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" customFormat="1" ht="87" spans="2:6">
+    <row r="23" customFormat="1" ht="90" spans="2:6">
       <c r="B23" s="4" t="s">
         <v>105</v>
       </c>
@@ -8837,7 +8910,7 @@
       </c>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" customFormat="1" ht="116" spans="2:6">
+    <row r="24" customFormat="1" ht="120" spans="2:6">
       <c r="B24" s="4" t="s">
         <v>88</v>
       </c>
@@ -8850,7 +8923,7 @@
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" customFormat="1" ht="72.5" spans="2:6">
+    <row r="25" customFormat="1" ht="75" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>84</v>
       </c>
@@ -8863,7 +8936,7 @@
       </c>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" customFormat="1" ht="29" spans="2:6">
+    <row r="26" customFormat="1" ht="30" spans="2:6">
       <c r="B26" s="4" t="s">
         <v>90</v>
       </c>
@@ -8874,7 +8947,7 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" customFormat="1" ht="29" spans="2:6">
+    <row r="27" customFormat="1" ht="30" spans="2:6">
       <c r="B27" s="4" t="s">
         <v>92</v>
       </c>
@@ -8885,7 +8958,7 @@
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" customFormat="1" ht="29" spans="2:6">
+    <row r="28" customFormat="1" ht="30" spans="2:6">
       <c r="B28" s="4" t="s">
         <v>94</v>
       </c>
@@ -8896,7 +8969,7 @@
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" customFormat="1" ht="29" spans="2:6">
+    <row r="29" customFormat="1" ht="30" spans="2:6">
       <c r="B29" s="4" t="s">
         <v>96</v>
       </c>
@@ -8907,7 +8980,7 @@
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" customFormat="1" ht="29" spans="2:6">
+    <row r="30" customFormat="1" ht="30" spans="2:6">
       <c r="B30" s="4" t="s">
         <v>98</v>
       </c>
@@ -8956,13 +9029,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="33.8818181818182" customWidth="1"/>
-    <col min="3" max="3" width="46.8545454545455" customWidth="1"/>
-    <col min="4" max="4" width="57.1181818181818" customWidth="1"/>
-    <col min="5" max="5" width="54.7181818181818" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="33.8857142857143" customWidth="1"/>
+    <col min="3" max="3" width="46.8571428571429" customWidth="1"/>
+    <col min="4" max="4" width="57.1142857142857" customWidth="1"/>
+    <col min="5" max="5" width="54.7142857142857" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8986,7 +9059,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" ht="43.5" spans="1:1">
+    <row r="2" ht="45" spans="1:1">
       <c r="A2" s="20" t="s">
         <v>348</v>
       </c>
@@ -9024,7 +9097,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" ht="29" spans="2:6">
+    <row r="6" ht="30" spans="2:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
@@ -9046,7 +9119,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="145" spans="2:5">
+    <row r="8" ht="150" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9071,7 +9144,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="10" ht="29" spans="2:4">
+    <row r="10" ht="30" spans="2:4">
       <c r="B10" s="5" t="s">
         <v>359</v>
       </c>
@@ -9090,7 +9163,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="29" spans="2:4">
+    <row r="12" ht="30" spans="2:4">
       <c r="B12" s="5" t="s">
         <v>362</v>
       </c>
@@ -9110,7 +9183,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="14" ht="29" spans="2:4">
+    <row r="14" ht="30" spans="2:4">
       <c r="B14" s="4" t="s">
         <v>366</v>
       </c>
@@ -9131,7 +9204,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="16" ht="58" spans="2:4">
+    <row r="16" ht="75" spans="2:4">
       <c r="B16" s="5" t="s">
         <v>269</v>
       </c>
@@ -9142,7 +9215,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="17" ht="29" spans="2:3">
+    <row r="17" ht="30" spans="2:3">
       <c r="B17" s="5" t="s">
         <v>271</v>
       </c>
@@ -9150,7 +9223,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="18" ht="87" spans="2:5">
+    <row r="18" ht="90" spans="2:5">
       <c r="B18" t="s">
         <v>371</v>
       </c>
@@ -9210,14 +9283,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="34.5727272727273" customWidth="1"/>
-    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
-    <col min="4" max="4" width="56.5545454545455" customWidth="1"/>
-    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
-    <col min="6" max="6" width="50.2818181818182" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="34.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="56.552380952381" customWidth="1"/>
+    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="50.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -9261,7 +9334,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" ht="82.5" spans="1:4">
+    <row r="4" ht="78" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -9285,7 +9358,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
@@ -9307,7 +9380,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="101.5" spans="2:5">
+    <row r="8" ht="105" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9332,7 +9405,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="10" ht="43.5" spans="2:5">
+    <row r="10" ht="45" spans="2:5">
       <c r="B10" s="5" t="s">
         <v>219</v>
       </c>
@@ -9344,7 +9417,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="11" ht="203" spans="2:5">
+    <row r="11" ht="210" spans="2:5">
       <c r="B11" s="5" t="s">
         <v>214</v>
       </c>
@@ -9353,7 +9426,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="12" ht="203" spans="2:5">
+    <row r="12" ht="210" spans="2:5">
       <c r="B12" s="5" t="s">
         <v>217</v>
       </c>
@@ -9403,7 +9476,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="9"/>
     </row>
-    <row r="17" ht="29" spans="2:5">
+    <row r="17" ht="30" spans="2:5">
       <c r="B17" s="5" t="s">
         <v>362</v>
       </c>
@@ -9415,7 +9488,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="18" ht="101.5" spans="2:5">
+    <row r="18" ht="105" spans="2:5">
       <c r="B18" s="4" t="s">
         <v>363</v>
       </c>
@@ -9429,7 +9502,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="19" ht="29" spans="2:3">
+    <row r="19" ht="30" spans="2:3">
       <c r="B19" s="4" t="s">
         <v>366</v>
       </c>
@@ -9437,7 +9510,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="20" ht="29" spans="2:3">
+    <row r="20" ht="30" spans="2:3">
       <c r="B20" s="4" t="s">
         <v>368</v>
       </c>
@@ -9457,7 +9530,7 @@
       </c>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" ht="72.5" spans="2:5">
+    <row r="22" ht="75" spans="2:5">
       <c r="B22" s="5" t="s">
         <v>404</v>
       </c>
@@ -9469,7 +9542,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="23" ht="43.5" spans="2:5">
+    <row r="23" ht="45" spans="2:5">
       <c r="B23" s="5" t="s">
         <v>407</v>
       </c>
@@ -9478,7 +9551,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="24" ht="58" spans="2:4">
+    <row r="24" ht="75" spans="2:4">
       <c r="B24" s="5" t="s">
         <v>269</v>
       </c>
@@ -9489,7 +9562,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="25" ht="29" spans="2:3">
+    <row r="25" ht="30" spans="2:3">
       <c r="B25" s="5" t="s">
         <v>271</v>
       </c>
@@ -9497,7 +9570,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="26" ht="43.5" spans="2:4">
+    <row r="26" ht="45" spans="2:4">
       <c r="B26" s="5" t="s">
         <v>409</v>
       </c>
@@ -9508,7 +9581,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="27" ht="188.5" spans="2:5">
+    <row r="27" ht="210" spans="2:5">
       <c r="B27" s="5" t="s">
         <v>371</v>
       </c>
@@ -9520,7 +9593,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="28" ht="43.5" spans="2:4">
+    <row r="28" ht="45" spans="2:4">
       <c r="B28" s="5" t="s">
         <v>413</v>
       </c>
@@ -9580,14 +9653,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="33.5727272727273" customWidth="1"/>
-    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
-    <col min="4" max="4" width="56.5545454545455" customWidth="1"/>
-    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
-    <col min="6" max="6" width="47.5727272727273" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="33.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="56.552380952381" customWidth="1"/>
+    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="47.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -9655,7 +9728,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
@@ -9680,7 +9753,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="101.5" spans="2:5">
+    <row r="8" ht="105" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9705,7 +9778,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="10" ht="145" spans="2:5">
+    <row r="10" ht="150" spans="2:5">
       <c r="B10" s="5" t="s">
         <v>356</v>
       </c>
@@ -9719,7 +9792,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="11" ht="159.5" spans="2:5">
+    <row r="11" ht="180" spans="2:5">
       <c r="B11" s="5" t="s">
         <v>359</v>
       </c>
@@ -9728,7 +9801,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="12" ht="145" spans="2:5">
+    <row r="12" ht="150" spans="2:5">
       <c r="B12" s="5" t="s">
         <v>361</v>
       </c>
@@ -9737,7 +9810,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="13" ht="58" spans="2:4">
+    <row r="13" ht="75" spans="2:4">
       <c r="B13" s="5" t="s">
         <v>269</v>
       </c>
@@ -9748,7 +9821,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="14" ht="29" spans="2:3">
+    <row r="14" ht="30" spans="2:3">
       <c r="B14" s="5" t="s">
         <v>271</v>
       </c>
@@ -9756,7 +9829,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="15" ht="43.5" spans="2:4">
+    <row r="15" ht="45" spans="2:4">
       <c r="B15" s="5" t="s">
         <v>409</v>
       </c>
@@ -9767,7 +9840,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="16" ht="188.5" spans="2:5">
+    <row r="16" ht="210" spans="2:5">
       <c r="B16" s="5" t="s">
         <v>371</v>
       </c>
@@ -9779,7 +9852,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="17" ht="43.5" spans="2:4">
+    <row r="17" ht="45" spans="2:4">
       <c r="B17" s="5" t="s">
         <v>413</v>
       </c>
@@ -9804,7 +9877,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="19" ht="159.5" spans="2:5">
+    <row r="19" ht="165" spans="2:5">
       <c r="B19" t="s">
         <v>426</v>
       </c>

--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - Medent.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - Medent.xlsx
@@ -688,6 +688,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">If </t>
     </r>
     <r>
@@ -3503,7 +3510,7 @@
     <t>name</t>
   </si>
   <si>
-    <t>ClinicalDocument.component.structuredBody.component.section[@ID='encounters'].entry[1].encounter.participant[@typeCode='LOC'].participantRole[@classCode='SDLOC'].playingEntity.name</t>
+    <t>ClinicalDocument.component.structuredBody.component.section[code[@code='46240-8']].entry[1].encounter.participant[@typeCode='LOC'].participantRole[@classCode='SDLOC'].playingEntity.name</t>
   </si>
   <si>
     <t>"name" : "Care Ridge SCN",</t>
@@ -5621,6 +5628,7 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5628,7 +5636,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5637,14 +5660,6 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5674,14 +5689,6 @@
       <color rgb="FF00B050"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
@@ -6265,7 +6272,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -6793,7 +6800,7 @@
     <col min="3" max="3" width="92.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:3">
       <c r="B1" s="32" t="s">
         <v>0</v>
       </c>
@@ -6873,7 +6880,7 @@
     <col min="6" max="6" width="57.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -6893,7 +6900,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" customFormat="1" spans="1:5">
+    <row r="2" customFormat="1" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>47</v>
       </c>
@@ -6904,7 +6911,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" customFormat="1" spans="2:3">
+    <row r="3" customFormat="1" spans="1:7">
       <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
@@ -6912,7 +6919,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="60" spans="2:7">
+    <row r="4" customFormat="1" ht="60" spans="1:7">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -6926,7 +6933,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" customFormat="1" spans="2:5">
+    <row r="5" customFormat="1" spans="1:7">
       <c r="B5" s="5" t="s">
         <v>19</v>
       </c>
@@ -6936,7 +6943,7 @@
       <c r="D5"/>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="1:7">
       <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
@@ -6951,7 +6958,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="2:6">
+    <row r="7" customFormat="1" spans="1:7">
       <c r="B7" s="5" t="s">
         <v>324</v>
       </c>
@@ -6964,7 +6971,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" customFormat="1" ht="75" spans="2:5">
+    <row r="8" customFormat="1" ht="75" spans="1:7">
       <c r="B8" s="4" t="s">
         <v>84</v>
       </c>
@@ -6978,7 +6985,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="9" customFormat="1" ht="60" spans="2:5">
+    <row r="9" customFormat="1" ht="60" spans="1:7">
       <c r="B9" s="4" t="s">
         <v>88</v>
       </c>
@@ -6988,7 +6995,7 @@
       <c r="D9" s="12"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" customFormat="1" spans="2:5">
+    <row r="10" customFormat="1" spans="1:7">
       <c r="B10" s="4" t="s">
         <v>90</v>
       </c>
@@ -6998,7 +7005,7 @@
       <c r="D10" s="12"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" customFormat="1" spans="2:5">
+    <row r="11" customFormat="1" spans="1:7">
       <c r="B11" s="4" t="s">
         <v>92</v>
       </c>
@@ -7008,7 +7015,7 @@
       <c r="D11" s="12"/>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" customFormat="1" spans="2:5">
+    <row r="12" customFormat="1" spans="1:7">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
@@ -7018,7 +7025,7 @@
       <c r="D12" s="12"/>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" customFormat="1" spans="2:5">
+    <row r="13" customFormat="1" spans="1:7">
       <c r="B13" s="4" t="s">
         <v>96</v>
       </c>
@@ -7028,7 +7035,7 @@
       <c r="D13" s="12"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" customFormat="1" spans="2:5">
+    <row r="14" customFormat="1" spans="1:7">
       <c r="B14" s="4" t="s">
         <v>98</v>
       </c>
@@ -7038,7 +7045,7 @@
       <c r="D14" s="12"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" customFormat="1" spans="2:5">
+    <row r="15" customFormat="1" spans="1:7">
       <c r="B15" s="4" t="s">
         <v>445</v>
       </c>
@@ -7048,7 +7055,7 @@
       <c r="D15" s="12"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" customFormat="1" spans="2:6">
+    <row r="16" customFormat="1" spans="1:7">
       <c r="B16" s="4" t="s">
         <v>192</v>
       </c>
@@ -7117,12 +7124,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" customFormat="1" spans="1:3">
+    <row r="3" customFormat="1" spans="1:6">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
         <v>14</v>
@@ -7131,7 +7138,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" customFormat="1" spans="1:4">
+    <row r="4" customFormat="1" spans="1:6">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
         <v>16</v>
@@ -7143,7 +7150,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" s="26" customFormat="1" ht="61" customHeight="1" spans="1:4">
+    <row r="5" s="26" customFormat="1" ht="61" customHeight="1" spans="1:6">
       <c r="A5" s="27"/>
       <c r="B5" s="27" t="s">
         <v>19</v>
@@ -7155,7 +7162,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" s="26" customFormat="1" ht="49" customHeight="1" spans="1:4">
+    <row r="6" s="26" customFormat="1" ht="49" customHeight="1" spans="1:6">
       <c r="A6" s="27"/>
       <c r="B6" s="27" t="s">
         <v>22</v>
@@ -7165,7 +7172,7 @@
       </c>
       <c r="D6" s="28"/>
     </row>
-    <row r="7" s="26" customFormat="1" ht="86" customHeight="1" spans="1:4">
+    <row r="7" s="26" customFormat="1" ht="86" customHeight="1" spans="1:6">
       <c r="A7" s="27"/>
       <c r="B7" s="27" t="s">
         <v>24</v>
@@ -7175,7 +7182,7 @@
       </c>
       <c r="D7" s="28"/>
     </row>
-    <row r="8" customFormat="1" spans="2:4">
+    <row r="8" customFormat="1" spans="1:6">
       <c r="B8" t="s">
         <v>26</v>
       </c>
@@ -7184,7 +7191,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" customFormat="1" spans="2:3">
+    <row r="9" customFormat="1" spans="1:6">
       <c r="B9" t="s">
         <v>28</v>
       </c>
@@ -7192,7 +7199,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="30" spans="2:3">
+    <row r="10" customFormat="1" ht="30" spans="1:6">
       <c r="B10" t="s">
         <v>30</v>
       </c>
@@ -7200,12 +7207,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="2:3">
+    <row r="15" spans="1:6">
       <c r="B15" t="s">
         <v>33</v>
       </c>
@@ -7213,7 +7220,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" ht="75" spans="2:3">
+    <row r="16" ht="75" spans="1:6">
       <c r="B16" t="s">
         <v>35</v>
       </c>
@@ -7221,7 +7228,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="2:3">
+    <row r="17" spans="2:5">
       <c r="B17" t="s">
         <v>37</v>
       </c>
@@ -7264,7 +7271,7 @@
       </c>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" ht="45" spans="2:3">
+    <row r="22" ht="45" spans="2:5">
       <c r="B22" s="30" t="s">
         <v>47</v>
       </c>
@@ -7318,12 +7325,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:6">
       <c r="A3" s="1"/>
       <c r="B3" s="4" t="s">
         <v>14</v>
@@ -7332,7 +7339,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="1:6">
       <c r="B4" s="15" t="s">
         <v>16</v>
       </c>
@@ -7343,7 +7350,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:6">
       <c r="A5" s="1"/>
       <c r="B5" s="15" t="s">
         <v>19</v>
@@ -7352,7 +7359,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="2:3">
+    <row r="6" spans="1:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
@@ -7360,7 +7367,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" ht="30" spans="2:4">
+    <row r="7" ht="30" spans="1:6">
       <c r="B7" s="4" t="s">
         <v>55</v>
       </c>
@@ -7371,7 +7378,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" ht="60" spans="2:5">
+    <row r="8" ht="60" spans="1:6">
       <c r="B8" s="4" t="s">
         <v>58</v>
       </c>
@@ -7385,7 +7392,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="1:6">
       <c r="B9" s="10" t="s">
         <v>62</v>
       </c>
@@ -7394,7 +7401,7 @@
       </c>
       <c r="D9" s="10"/>
     </row>
-    <row r="10" spans="2:4">
+    <row r="10" spans="1:6">
       <c r="B10" s="4" t="s">
         <v>64</v>
       </c>
@@ -7405,7 +7412,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="2:4">
+    <row r="11" spans="1:6">
       <c r="B11" s="15" t="s">
         <v>67</v>
       </c>
@@ -7416,7 +7423,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="2:4">
+    <row r="12" spans="1:6">
       <c r="B12" s="15" t="s">
         <v>70</v>
       </c>
@@ -7427,7 +7434,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" ht="60" spans="2:4">
+    <row r="13" ht="60" spans="1:6">
       <c r="B13" s="4" t="s">
         <v>72</v>
       </c>
@@ -7438,7 +7445,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:4">
+    <row r="14" ht="30" spans="1:6">
       <c r="B14" s="4" t="s">
         <v>75</v>
       </c>
@@ -7449,7 +7456,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" ht="30" spans="2:4">
+    <row r="15" ht="30" spans="1:6">
       <c r="B15" s="4" t="s">
         <v>78</v>
       </c>
@@ -7460,7 +7467,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="2:4">
+    <row r="16" spans="1:6">
       <c r="B16" s="15" t="s">
         <v>81</v>
       </c>
@@ -7485,7 +7492,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" ht="60" spans="2:4">
+    <row r="18" ht="60" spans="2:5">
       <c r="B18" s="4" t="s">
         <v>88</v>
       </c>
@@ -7494,7 +7501,7 @@
       </c>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4">
+    <row r="19" spans="2:5">
       <c r="B19" s="4" t="s">
         <v>90</v>
       </c>
@@ -7503,7 +7510,7 @@
       </c>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:5">
       <c r="B20" s="4" t="s">
         <v>92</v>
       </c>
@@ -7512,7 +7519,7 @@
       </c>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4">
+    <row r="21" spans="2:5">
       <c r="B21" s="4" t="s">
         <v>94</v>
       </c>
@@ -7521,7 +7528,7 @@
       </c>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4">
+    <row r="22" spans="2:5">
       <c r="B22" s="4" t="s">
         <v>96</v>
       </c>
@@ -7530,7 +7537,7 @@
       </c>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4">
+    <row r="23" spans="2:5">
       <c r="B23" s="4" t="s">
         <v>98</v>
       </c>
@@ -7550,7 +7557,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="2:3">
+    <row r="25" spans="2:5">
       <c r="B25" s="4" t="s">
         <v>103</v>
       </c>
@@ -7637,7 +7644,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="33" ht="30" spans="2:4">
+    <row r="33" ht="30" spans="2:6">
       <c r="B33" s="4" t="s">
         <v>112</v>
       </c>
@@ -7646,7 +7653,7 @@
       </c>
       <c r="D33" s="14"/>
     </row>
-    <row r="34" spans="2:4">
+    <row r="34" spans="2:6">
       <c r="B34" s="4" t="s">
         <v>114</v>
       </c>
@@ -7655,7 +7662,7 @@
       </c>
       <c r="D34" s="14"/>
     </row>
-    <row r="35" ht="30" spans="2:4">
+    <row r="35" ht="30" spans="2:6">
       <c r="B35" s="4" t="s">
         <v>116</v>
       </c>
@@ -7664,7 +7671,7 @@
       </c>
       <c r="D35" s="14"/>
     </row>
-    <row r="36" spans="2:4">
+    <row r="36" spans="2:6">
       <c r="B36" s="4" t="s">
         <v>118</v>
       </c>
@@ -7673,7 +7680,7 @@
       </c>
       <c r="D36" s="14"/>
     </row>
-    <row r="37" spans="2:4">
+    <row r="37" spans="2:6">
       <c r="B37" s="4" t="s">
         <v>118</v>
       </c>
@@ -7684,7 +7691,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="38" ht="45" spans="2:5">
+    <row r="38" ht="45" spans="2:6">
       <c r="B38" s="4" t="s">
         <v>128</v>
       </c>
@@ -7718,7 +7725,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="41" spans="2:4">
+    <row r="41" spans="2:6">
       <c r="B41" s="15" t="s">
         <v>136</v>
       </c>
@@ -7727,7 +7734,7 @@
       </c>
       <c r="D41" s="10"/>
     </row>
-    <row r="42" spans="2:4">
+    <row r="42" spans="2:6">
       <c r="B42" s="15" t="s">
         <v>138</v>
       </c>
@@ -7736,7 +7743,7 @@
       </c>
       <c r="D42" s="10"/>
     </row>
-    <row r="43" spans="2:4">
+    <row r="43" spans="2:6">
       <c r="B43" s="15" t="s">
         <v>140</v>
       </c>
@@ -7745,7 +7752,7 @@
       </c>
       <c r="D43" s="10"/>
     </row>
-    <row r="44" spans="2:4">
+    <row r="44" spans="2:6">
       <c r="B44" s="4" t="s">
         <v>142</v>
       </c>
@@ -7754,7 +7761,7 @@
       </c>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" ht="195" spans="2:5">
+    <row r="45" ht="195" spans="2:6">
       <c r="B45" s="15" t="s">
         <v>143</v>
       </c>
@@ -7768,7 +7775,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="46" ht="195" spans="2:5">
+    <row r="46" ht="195" spans="2:6">
       <c r="B46" s="15" t="s">
         <v>147</v>
       </c>
@@ -7782,7 +7789,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" ht="195" spans="2:5">
+    <row r="47" ht="195" spans="2:6">
       <c r="B47" s="15" t="s">
         <v>151</v>
       </c>
@@ -7794,7 +7801,7 @@
       </c>
       <c r="E47" s="24"/>
     </row>
-    <row r="48" customFormat="1" spans="2:5">
+    <row r="48" customFormat="1" spans="2:6">
       <c r="B48" s="4" t="s">
         <v>154</v>
       </c>
@@ -7804,7 +7811,7 @@
       <c r="D48" s="10"/>
       <c r="E48" s="4"/>
     </row>
-    <row r="49" customFormat="1" spans="2:5">
+    <row r="49" customFormat="1" spans="2:6">
       <c r="B49" s="4" t="s">
         <v>155</v>
       </c>
@@ -7814,7 +7821,7 @@
       <c r="D49" s="10"/>
       <c r="E49" s="4"/>
     </row>
-    <row r="50" customFormat="1" spans="2:5">
+    <row r="50" customFormat="1" spans="2:6">
       <c r="B50" s="4" t="s">
         <v>157</v>
       </c>
@@ -7824,7 +7831,7 @@
       <c r="D50" s="10"/>
       <c r="E50" s="4"/>
     </row>
-    <row r="51" customFormat="1" spans="2:5">
+    <row r="51" customFormat="1" spans="2:6">
       <c r="B51" s="4" t="s">
         <v>159</v>
       </c>
@@ -7834,7 +7841,7 @@
       <c r="D51" s="10"/>
       <c r="E51" s="4"/>
     </row>
-    <row r="52" ht="150" spans="2:5">
+    <row r="52" ht="150" spans="2:6">
       <c r="B52" s="10" t="s">
         <v>160</v>
       </c>
@@ -7848,7 +7855,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="53" spans="2:5">
+    <row r="53" spans="2:6">
       <c r="B53" s="4" t="s">
         <v>164</v>
       </c>
@@ -7858,7 +7865,7 @@
       <c r="D53" s="10"/>
       <c r="E53" s="8"/>
     </row>
-    <row r="54" customFormat="1" spans="2:5">
+    <row r="54" customFormat="1" spans="2:6">
       <c r="B54" s="4" t="s">
         <v>166</v>
       </c>
@@ -7868,7 +7875,7 @@
       <c r="D54" s="10"/>
       <c r="E54" s="8"/>
     </row>
-    <row r="55" customFormat="1" spans="2:5">
+    <row r="55" customFormat="1" spans="2:6">
       <c r="B55" s="4" t="s">
         <v>167</v>
       </c>
@@ -7878,7 +7885,7 @@
       <c r="D55" s="10"/>
       <c r="E55" s="8"/>
     </row>
-    <row r="56" customFormat="1" spans="2:5">
+    <row r="56" customFormat="1" spans="2:6">
       <c r="B56" s="4" t="s">
         <v>169</v>
       </c>
@@ -7888,7 +7895,7 @@
       <c r="D56" s="10"/>
       <c r="E56" s="8"/>
     </row>
-    <row r="57" customFormat="1" spans="2:5">
+    <row r="57" customFormat="1" spans="2:6">
       <c r="B57" s="4" t="s">
         <v>171</v>
       </c>
@@ -7898,7 +7905,7 @@
       <c r="D57" s="10"/>
       <c r="E57" s="8"/>
     </row>
-    <row r="58" spans="2:5">
+    <row r="58" spans="2:6">
       <c r="B58" s="4" t="s">
         <v>172</v>
       </c>
@@ -7908,7 +7915,7 @@
       <c r="D58" s="10"/>
       <c r="E58" s="8"/>
     </row>
-    <row r="59" ht="180" spans="2:5">
+    <row r="59" ht="180" spans="2:6">
       <c r="B59" s="10" t="s">
         <v>174</v>
       </c>
@@ -8041,7 +8048,7 @@
     <col min="6" max="6" width="57.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -8061,7 +8068,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" ht="33" customHeight="1" spans="1:5">
+    <row r="2" ht="33" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>39</v>
       </c>
@@ -8072,7 +8079,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="1:7">
       <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
@@ -8080,7 +8087,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" ht="60" spans="2:7">
+    <row r="4" ht="60" spans="1:7">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -8093,7 +8100,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="1:7">
       <c r="B5" s="5" t="s">
         <v>19</v>
       </c>
@@ -8102,7 +8109,7 @@
       </c>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" spans="1:7">
       <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
@@ -8111,7 +8118,7 @@
       </c>
       <c r="E6" s="25"/>
     </row>
-    <row r="7" ht="120" spans="2:6">
+    <row r="7" ht="120" spans="1:7">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
@@ -8126,7 +8133,7 @@
       </c>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" ht="94" customHeight="1" spans="2:5">
+    <row r="8" ht="94" customHeight="1" spans="1:7">
       <c r="B8" s="5" t="s">
         <v>206</v>
       </c>
@@ -8140,7 +8147,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="2:5">
+    <row r="9" customFormat="1" spans="1:7">
       <c r="B9" s="5" t="s">
         <v>210</v>
       </c>
@@ -8152,7 +8159,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="10" spans="2:5">
+    <row r="10" spans="1:7">
       <c r="B10" s="5" t="s">
         <v>212</v>
       </c>
@@ -8164,7 +8171,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="11" ht="225" spans="2:5">
+    <row r="11" ht="225" spans="1:7">
       <c r="B11" s="5" t="s">
         <v>214</v>
       </c>
@@ -8178,7 +8185,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="12" spans="2:5">
+    <row r="12" spans="1:7">
       <c r="B12" s="5" t="s">
         <v>217</v>
       </c>
@@ -8189,7 +8196,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="13" spans="2:5">
+    <row r="13" spans="1:7">
       <c r="B13" s="5" t="s">
         <v>219</v>
       </c>
@@ -8200,7 +8207,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:5">
+    <row r="14" ht="30" spans="1:7">
       <c r="B14" s="5" t="s">
         <v>221</v>
       </c>
@@ -8214,7 +8221,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="15" ht="120" spans="2:5">
+    <row r="15" ht="120" spans="1:7">
       <c r="B15" s="5" t="s">
         <v>225</v>
       </c>
@@ -8228,7 +8235,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="16" ht="45" spans="2:5">
+    <row r="16" ht="45" spans="1:7">
       <c r="B16" s="5" t="s">
         <v>229</v>
       </c>
@@ -8240,7 +8247,7 @@
       </c>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" ht="45" spans="2:5">
+    <row r="17" ht="45" spans="2:6">
       <c r="B17" s="5" t="s">
         <v>232</v>
       </c>
@@ -8252,7 +8259,7 @@
       </c>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" ht="45" spans="2:5">
+    <row r="18" ht="45" spans="2:6">
       <c r="B18" t="s">
         <v>235</v>
       </c>
@@ -8266,7 +8273,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="19" ht="60" spans="2:5">
+    <row r="19" ht="60" spans="2:6">
       <c r="B19" s="5" t="s">
         <v>238</v>
       </c>
@@ -8280,7 +8287,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="20" customFormat="1" spans="2:5">
+    <row r="20" customFormat="1" spans="2:6">
       <c r="B20" s="5" t="s">
         <v>241</v>
       </c>
@@ -8361,7 +8368,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1" spans="1:5">
+    <row r="2" ht="17" customHeight="1" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>35</v>
       </c>
@@ -8372,7 +8379,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" customFormat="1" spans="2:3">
+    <row r="3" customFormat="1" spans="1:6">
       <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
@@ -8380,7 +8387,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="4" ht="60" spans="1:5">
+    <row r="4" ht="60" spans="1:6">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -8407,7 +8414,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="1:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
@@ -8418,7 +8425,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" ht="165" spans="2:5">
+    <row r="7" ht="165" spans="1:6">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
@@ -8432,7 +8439,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="8" ht="71" customHeight="1" spans="2:5">
+    <row r="8" ht="71" customHeight="1" spans="1:6">
       <c r="B8" s="5" t="s">
         <v>253</v>
       </c>
@@ -8444,7 +8451,7 @@
       </c>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" ht="30" spans="2:5">
+    <row r="9" ht="30" spans="1:6">
       <c r="B9" s="5" t="s">
         <v>256</v>
       </c>
@@ -8454,7 +8461,7 @@
       <c r="D9" s="10"/>
       <c r="E9" s="24"/>
     </row>
-    <row r="10" spans="2:5">
+    <row r="10" spans="1:6">
       <c r="B10" s="5" t="s">
         <v>258</v>
       </c>
@@ -8464,7 +8471,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" ht="30" spans="2:4">
+    <row r="11" ht="30" spans="1:6">
       <c r="B11" s="5" t="s">
         <v>260</v>
       </c>
@@ -8475,7 +8482,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="12" ht="60" spans="2:5">
+    <row r="12" ht="60" spans="1:6">
       <c r="B12" s="5" t="s">
         <v>263</v>
       </c>
@@ -8484,7 +8491,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" ht="33" customHeight="1" spans="2:4">
+    <row r="13" ht="33" customHeight="1" spans="1:6">
       <c r="B13" s="5" t="s">
         <v>265</v>
       </c>
@@ -8493,7 +8500,7 @@
       </c>
       <c r="D13" s="12"/>
     </row>
-    <row r="14" customFormat="1" spans="2:3">
+    <row r="14" customFormat="1" spans="1:6">
       <c r="B14" t="s">
         <v>267</v>
       </c>
@@ -8501,7 +8508,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="60" spans="2:4">
+    <row r="15" customFormat="1" ht="60" spans="1:6">
       <c r="B15" s="5" t="s">
         <v>269</v>
       </c>
@@ -8512,7 +8519,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="30" spans="2:3">
+    <row r="16" customFormat="1" ht="30" spans="1:6">
       <c r="B16" s="5" t="s">
         <v>271</v>
       </c>
@@ -8520,7 +8527,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="17" ht="60" spans="2:4">
+    <row r="17" ht="60" spans="2:5">
       <c r="B17" t="s">
         <v>273</v>
       </c>
@@ -8531,7 +8538,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="18" spans="2:3">
+    <row r="18" spans="2:5">
       <c r="B18" t="s">
         <v>276</v>
       </c>
@@ -8604,7 +8611,7 @@
       <c r="D24" s="10"/>
       <c r="E24" s="4"/>
     </row>
-    <row r="25" customFormat="1" spans="2:4">
+    <row r="25" customFormat="1" spans="2:5">
       <c r="B25" s="4" t="s">
         <v>192</v>
       </c>
@@ -8615,7 +8622,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="26" customFormat="1" ht="46" customHeight="1" spans="2:4">
+    <row r="26" customFormat="1" ht="46" customHeight="1" spans="2:5">
       <c r="B26" s="4" t="s">
         <v>195</v>
       </c>
@@ -8672,12 +8679,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" customFormat="1" spans="2:3">
+    <row r="3" customFormat="1" spans="1:6">
       <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
@@ -8685,7 +8692,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="4" spans="2:3">
+    <row r="4" spans="1:6">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -8707,7 +8714,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="1:6">
       <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
@@ -8718,7 +8725,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="1:6">
       <c r="B7" s="5" t="s">
         <v>299</v>
       </c>
@@ -8732,7 +8739,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="8" ht="63" customHeight="1" spans="2:6">
+    <row r="8" ht="63" customHeight="1" spans="1:6">
       <c r="B8" t="s">
         <v>303</v>
       </c>
@@ -8746,7 +8753,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="9" spans="2:5">
+    <row r="9" spans="1:6">
       <c r="B9" t="s">
         <v>307</v>
       </c>
@@ -8756,7 +8763,7 @@
       <c r="D9" s="10"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" ht="30" spans="2:5">
+    <row r="10" ht="30" spans="1:6">
       <c r="B10" s="4" t="s">
         <v>309</v>
       </c>
@@ -8766,7 +8773,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" ht="30" spans="2:5">
+    <row r="11" ht="30" spans="1:6">
       <c r="B11" s="4" t="s">
         <v>311</v>
       </c>
@@ -8776,7 +8783,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="30" spans="2:5">
+    <row r="12" ht="30" spans="1:6">
       <c r="B12" s="4" t="s">
         <v>312</v>
       </c>
@@ -8786,7 +8793,7 @@
       <c r="D12" s="10"/>
       <c r="E12" s="8"/>
     </row>
-    <row r="13" customFormat="1" ht="66" customHeight="1" spans="2:6">
+    <row r="13" customFormat="1" ht="66" customHeight="1" spans="1:6">
       <c r="B13" t="s">
         <v>314</v>
       </c>
@@ -8800,7 +8807,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="14" customFormat="1" spans="2:5">
+    <row r="14" customFormat="1" spans="1:6">
       <c r="B14" t="s">
         <v>317</v>
       </c>
@@ -8810,7 +8817,7 @@
       <c r="D14" s="10"/>
       <c r="E14" s="21"/>
     </row>
-    <row r="15" customFormat="1" ht="30" spans="2:5">
+    <row r="15" customFormat="1" ht="30" spans="1:6">
       <c r="B15" s="4" t="s">
         <v>319</v>
       </c>
@@ -8820,7 +8827,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="21"/>
     </row>
-    <row r="16" customFormat="1" ht="30" spans="2:5">
+    <row r="16" customFormat="1" ht="30" spans="1:6">
       <c r="B16" s="4" t="s">
         <v>321</v>
       </c>
@@ -8830,7 +8837,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" customFormat="1" ht="30" spans="2:4">
+    <row r="17" customFormat="1" ht="30" spans="2:6">
       <c r="B17" s="4" t="s">
         <v>322</v>
       </c>
@@ -8839,7 +8846,7 @@
       </c>
       <c r="D17" s="10"/>
     </row>
-    <row r="18" ht="60" spans="2:5">
+    <row r="18" ht="60" spans="2:6">
       <c r="B18" s="5" t="s">
         <v>324</v>
       </c>
@@ -8991,7 +8998,7 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" customFormat="1" spans="2:4">
+    <row r="31" customFormat="1" spans="2:6">
       <c r="B31" s="4" t="s">
         <v>192</v>
       </c>
@@ -9002,7 +9009,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="32" customFormat="1" ht="46" customHeight="1" spans="2:4">
+    <row r="32" customFormat="1" ht="46" customHeight="1" spans="2:6">
       <c r="B32" s="4" t="s">
         <v>195</v>
       </c>
@@ -9059,12 +9066,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" ht="45" spans="1:1">
+    <row r="2" ht="45" spans="1:6">
       <c r="A2" s="20" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:6">
       <c r="A3" s="1"/>
       <c r="B3" s="4" t="s">
         <v>14</v>
@@ -9073,7 +9080,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:6">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -9097,7 +9104,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" ht="30" spans="2:6">
+    <row r="6" ht="30" spans="1:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
@@ -9108,7 +9115,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="1:6">
       <c r="B7" t="s">
         <v>55</v>
       </c>
@@ -9119,7 +9126,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="150" spans="2:5">
+    <row r="8" ht="150" spans="1:6">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9133,7 +9140,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1" spans="2:4">
+    <row r="9" ht="70" customHeight="1" spans="1:6">
       <c r="B9" s="5" t="s">
         <v>356</v>
       </c>
@@ -9144,7 +9151,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="10" ht="30" spans="2:4">
+    <row r="10" ht="30" spans="1:6">
       <c r="B10" s="5" t="s">
         <v>359</v>
       </c>
@@ -9153,7 +9160,7 @@
       </c>
       <c r="D10" s="10"/>
     </row>
-    <row r="11" spans="2:5">
+    <row r="11" spans="1:6">
       <c r="B11" s="5" t="s">
         <v>361</v>
       </c>
@@ -9163,7 +9170,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="30" spans="2:4">
+    <row r="12" ht="30" spans="1:6">
       <c r="B12" s="5" t="s">
         <v>362</v>
       </c>
@@ -9172,7 +9179,7 @@
       </c>
       <c r="D12" s="10"/>
     </row>
-    <row r="13" ht="38" customHeight="1" spans="2:4">
+    <row r="13" ht="38" customHeight="1" spans="1:6">
       <c r="B13" s="4" t="s">
         <v>363</v>
       </c>
@@ -9183,7 +9190,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:4">
+    <row r="14" ht="30" spans="1:6">
       <c r="B14" s="4" t="s">
         <v>366</v>
       </c>
@@ -9192,7 +9199,7 @@
       </c>
       <c r="D14" s="10"/>
     </row>
-    <row r="15" ht="153" customHeight="1" spans="2:5">
+    <row r="15" ht="153" customHeight="1" spans="1:6">
       <c r="B15" s="4" t="s">
         <v>368</v>
       </c>
@@ -9204,7 +9211,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="16" ht="75" spans="2:4">
+    <row r="16" ht="75" spans="1:6">
       <c r="B16" s="5" t="s">
         <v>269</v>
       </c>
@@ -9215,7 +9222,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="17" ht="30" spans="2:3">
+    <row r="17" ht="30" spans="2:6">
       <c r="B17" s="5" t="s">
         <v>271</v>
       </c>
@@ -9223,7 +9230,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="18" ht="90" spans="2:5">
+    <row r="18" ht="90" spans="2:6">
       <c r="B18" t="s">
         <v>371</v>
       </c>
@@ -9248,7 +9255,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:6">
       <c r="B20" s="4" t="s">
         <v>192</v>
       </c>
@@ -9259,7 +9266,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="21" ht="45" customHeight="1" spans="2:4">
+    <row r="21" ht="45" customHeight="1" spans="2:6">
       <c r="B21" s="4" t="s">
         <v>195</v>
       </c>
@@ -9325,7 +9332,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="19"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:6">
       <c r="A3" s="1"/>
       <c r="B3" s="4" t="s">
         <v>14</v>
@@ -9334,7 +9341,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" ht="78" spans="1:4">
+    <row r="4" ht="78" spans="1:6">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -9358,7 +9365,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="1:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
@@ -9369,7 +9376,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="1:6">
       <c r="B7" t="s">
         <v>55</v>
       </c>
@@ -9380,7 +9387,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="105" spans="2:5">
+    <row r="8" ht="105" spans="1:6">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9394,7 +9401,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="9" ht="139" customHeight="1" spans="2:5">
+    <row r="9" ht="139" customHeight="1" spans="1:6">
       <c r="B9" s="5" t="s">
         <v>386</v>
       </c>
@@ -9405,7 +9412,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="10" ht="45" spans="2:5">
+    <row r="10" ht="45" spans="1:6">
       <c r="B10" s="5" t="s">
         <v>219</v>
       </c>
@@ -9417,7 +9424,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="11" ht="210" spans="2:5">
+    <row r="11" ht="210" spans="1:6">
       <c r="B11" s="5" t="s">
         <v>214</v>
       </c>
@@ -9426,7 +9433,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="12" ht="210" spans="2:5">
+    <row r="12" ht="210" spans="1:6">
       <c r="B12" s="5" t="s">
         <v>217</v>
       </c>
@@ -9435,7 +9442,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="13" spans="2:5">
+    <row r="13" spans="1:6">
       <c r="B13" s="5" t="s">
         <v>393</v>
       </c>
@@ -9444,7 +9451,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="14" ht="84" customHeight="1" spans="2:5">
+    <row r="14" ht="84" customHeight="1" spans="1:6">
       <c r="B14" s="5" t="s">
         <v>356</v>
       </c>
@@ -9456,7 +9463,7 @@
       </c>
       <c r="E14" s="9"/>
     </row>
-    <row r="15" spans="2:5">
+    <row r="15" spans="1:6">
       <c r="B15" s="5" t="s">
         <v>359</v>
       </c>
@@ -9466,7 +9473,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="9"/>
     </row>
-    <row r="16" spans="2:5">
+    <row r="16" spans="1:6">
       <c r="B16" s="5" t="s">
         <v>361</v>
       </c>
@@ -9476,7 +9483,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="9"/>
     </row>
-    <row r="17" ht="30" spans="2:5">
+    <row r="17" ht="30" spans="2:6">
       <c r="B17" s="5" t="s">
         <v>362</v>
       </c>
@@ -9488,7 +9495,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="18" ht="105" spans="2:5">
+    <row r="18" ht="105" spans="2:6">
       <c r="B18" s="4" t="s">
         <v>363</v>
       </c>
@@ -9502,7 +9509,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="19" ht="30" spans="2:3">
+    <row r="19" ht="30" spans="2:6">
       <c r="B19" s="4" t="s">
         <v>366</v>
       </c>
@@ -9510,7 +9517,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="20" ht="30" spans="2:3">
+    <row r="20" ht="30" spans="2:6">
       <c r="B20" s="4" t="s">
         <v>368</v>
       </c>
@@ -9518,7 +9525,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="21" ht="37" customHeight="1" spans="2:5">
+    <row r="21" ht="37" customHeight="1" spans="2:6">
       <c r="B21" s="5" t="s">
         <v>401</v>
       </c>
@@ -9530,7 +9537,7 @@
       </c>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" ht="75" spans="2:5">
+    <row r="22" ht="75" spans="2:6">
       <c r="B22" s="5" t="s">
         <v>404</v>
       </c>
@@ -9542,7 +9549,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="23" ht="45" spans="2:5">
+    <row r="23" ht="45" spans="2:6">
       <c r="B23" s="5" t="s">
         <v>407</v>
       </c>
@@ -9551,7 +9558,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="24" ht="75" spans="2:4">
+    <row r="24" ht="75" spans="2:6">
       <c r="B24" s="5" t="s">
         <v>269</v>
       </c>
@@ -9562,7 +9569,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="25" ht="30" spans="2:3">
+    <row r="25" ht="30" spans="2:6">
       <c r="B25" s="5" t="s">
         <v>271</v>
       </c>
@@ -9570,7 +9577,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="26" ht="45" spans="2:4">
+    <row r="26" ht="45" spans="2:6">
       <c r="B26" s="5" t="s">
         <v>409</v>
       </c>
@@ -9581,7 +9588,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="27" ht="210" spans="2:5">
+    <row r="27" ht="210" spans="2:6">
       <c r="B27" s="5" t="s">
         <v>371</v>
       </c>
@@ -9593,7 +9600,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="28" ht="45" spans="2:4">
+    <row r="28" ht="45" spans="2:6">
       <c r="B28" s="5" t="s">
         <v>413</v>
       </c>
@@ -9616,7 +9623,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="30" spans="2:4">
+    <row r="30" spans="2:6">
       <c r="B30" s="4" t="s">
         <v>192</v>
       </c>
@@ -9627,7 +9634,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="31" ht="46" customHeight="1" spans="2:4">
+    <row r="31" ht="46" customHeight="1" spans="2:6">
       <c r="B31" s="4" t="s">
         <v>195</v>
       </c>
@@ -9695,7 +9702,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:6">
       <c r="A3" s="1"/>
       <c r="B3" s="4" t="s">
         <v>14</v>
@@ -9704,7 +9711,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:6">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -9728,7 +9735,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="1:6">
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
@@ -9739,7 +9746,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="1:6">
       <c r="B7" t="s">
         <v>55</v>
       </c>
@@ -9753,7 +9760,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="105" spans="2:5">
+    <row r="8" ht="105" spans="1:6">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9767,7 +9774,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="9" ht="409" customHeight="1" spans="2:5">
+    <row r="9" ht="409" customHeight="1" spans="1:6">
       <c r="B9" s="5" t="s">
         <v>386</v>
       </c>
@@ -9778,7 +9785,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="10" ht="150" spans="2:5">
+    <row r="10" ht="150" spans="1:6">
       <c r="B10" s="5" t="s">
         <v>356</v>
       </c>
@@ -9792,7 +9799,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="11" ht="180" spans="2:5">
+    <row r="11" ht="180" spans="1:6">
       <c r="B11" s="5" t="s">
         <v>359</v>
       </c>
@@ -9801,7 +9808,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="12" ht="150" spans="2:5">
+    <row r="12" ht="150" spans="1:6">
       <c r="B12" s="5" t="s">
         <v>361</v>
       </c>
@@ -9810,7 +9817,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="13" ht="75" spans="2:4">
+    <row r="13" ht="75" spans="1:6">
       <c r="B13" s="5" t="s">
         <v>269</v>
       </c>
@@ -9821,7 +9828,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:3">
+    <row r="14" ht="30" spans="1:6">
       <c r="B14" s="5" t="s">
         <v>271</v>
       </c>
@@ -9829,7 +9836,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="15" ht="45" spans="2:4">
+    <row r="15" ht="45" spans="1:6">
       <c r="B15" s="5" t="s">
         <v>409</v>
       </c>
@@ -9840,7 +9847,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="16" ht="210" spans="2:5">
+    <row r="16" ht="210" spans="1:6">
       <c r="B16" s="5" t="s">
         <v>371</v>
       </c>
@@ -9852,7 +9859,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="17" ht="45" spans="2:4">
+    <row r="17" ht="45" spans="2:6">
       <c r="B17" s="5" t="s">
         <v>413</v>
       </c>
@@ -9877,7 +9884,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="19" ht="165" spans="2:5">
+    <row r="19" ht="165" spans="2:6">
       <c r="B19" t="s">
         <v>426</v>
       </c>
@@ -9888,7 +9895,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:6">
       <c r="B20" s="4" t="s">
         <v>192</v>
       </c>
@@ -9899,7 +9906,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="21" ht="46" customHeight="1" spans="2:4">
+    <row r="21" ht="46" customHeight="1" spans="2:6">
       <c r="B21" s="4" t="s">
         <v>195</v>
       </c>

--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - Medent.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - Medent.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Medent" sheetId="11" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="455">
   <si>
     <t>Medent CCDA</t>
   </si>
@@ -90,6 +90,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Randomly generated UUID which is used as the</t>
     </r>
     <r>
@@ -1136,6 +1143,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Document.recordTarget.patientRole.id.</t>
     </r>
     <r>
@@ -1543,27 +1557,6 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Document.recordTarget.patientRole.id.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>extension</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">{
         "type" : {
           "coding" : [{
@@ -1754,7 +1747,7 @@
     <t>maritalStatus -&gt; coding -&gt; system</t>
   </si>
   <si>
-    <t>"http://terminology.hl7.org/CodeSystem/v3-MaritalStatus"</t>
+    <t>If maritalStatus code is "UNK" then "http://terminology.hl7.org/CodeSystem/v3-NullFlavor", otherwise "http://terminology.hl7.org/CodeSystem/v3-MaritalStatus".</t>
   </si>
   <si>
     <t>maritalStatus -&gt; coding -&gt; code</t>
@@ -2519,6 +2512,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">For </t>
     </r>
     <r>
@@ -4835,7 +4835,8 @@
     </r>
   </si>
   <si>
-    <t>Facility ID (from the header variable `X-TechBD-Facility-ID`) + '-' + SHA-256 UUID generated using 
+    <t>Facility ID (from the header variable `X-TechBD-Facility-ID`) + '-' + 
+SHA-256 UUID generated using 
 1. Patient-MRN (the value set for 'identifier (MR) -&gt; value' of Patient Resource from Document.recordTarget.patientRole.id.extension)
 2. Value of the header variable 'X-TechBD-CIN'
 3. Grouper ScreeningCode 
@@ -5619,6 +5620,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF00B050"/>
@@ -5630,21 +5646,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -6112,7 +6113,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6165,9 +6166,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -6757,18 +6755,18 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="8.88571428571429" style="33"/>
+    <col min="1" max="1" width="8.88571428571429" style="32"/>
     <col min="2" max="2" width="35.2190476190476" customWidth="1"/>
     <col min="3" max="3" width="92.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="33" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="33">
+      <c r="A3" s="32">
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -6779,7 +6777,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="33">
+      <c r="A4" s="32">
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
@@ -6790,10 +6788,10 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="33">
+      <c r="A5" s="32">
         <v>3</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
@@ -6801,10 +6799,10 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="33">
+      <c r="A6" s="32">
         <v>4</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>3</v>
       </c>
       <c r="C6" t="s">
@@ -6812,10 +6810,10 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="33">
+      <c r="A7" s="32">
         <v>5</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="27" t="s">
         <v>3</v>
       </c>
       <c r="C7" t="s">
@@ -6867,7 +6865,7 @@
         <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -6878,7 +6876,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="135" spans="1:7">
@@ -6886,10 +6884,10 @@
         <v>16</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="D4" t="s">
         <v>437</v>
-      </c>
-      <c r="D4" t="s">
-        <v>438</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="8"/>
@@ -6900,7 +6898,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D5"/>
       <c r="E5" s="9"/>
@@ -6910,25 +6908,25 @@
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D6"/>
       <c r="E6" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>440</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:7">
       <c r="B7" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C7" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="D7" t="s">
         <v>442</v>
-      </c>
-      <c r="D7" t="s">
-        <v>443</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="4"/>
@@ -6938,13 +6936,13 @@
         <v>85</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>87</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9" customFormat="1" ht="60" spans="1:7">
@@ -6952,7 +6950,7 @@
         <v>89</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="4"/>
@@ -6962,7 +6960,7 @@
         <v>91</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="4"/>
@@ -6972,7 +6970,7 @@
         <v>93</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="4"/>
@@ -6982,7 +6980,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="4"/>
@@ -6992,7 +6990,7 @@
         <v>97</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="4"/>
@@ -7002,40 +7000,40 @@
         <v>99</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="4"/>
     </row>
     <row r="15" customFormat="1" spans="1:7">
       <c r="B15" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>452</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>453</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="4"/>
     </row>
     <row r="16" customFormat="1" spans="1:7">
       <c r="B16" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="D16" s="15" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="4"/>
     </row>
     <row r="17" customFormat="1" ht="60" customHeight="1" spans="2:6">
       <c r="B17" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="9"/>
@@ -7105,44 +7103,44 @@
       <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="27" t="s">
         <v>17</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" s="27" customFormat="1" ht="61" customHeight="1" spans="1:6">
-      <c r="A5" s="29"/>
-      <c r="B5" s="29" t="s">
+    <row r="5" s="26" customFormat="1" ht="61" customHeight="1" spans="1:6">
+      <c r="A5" s="28"/>
+      <c r="B5" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="29" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" s="27" customFormat="1" ht="49" customHeight="1" spans="1:6">
-      <c r="A6" s="29"/>
-      <c r="B6" s="29" t="s">
+    <row r="6" s="26" customFormat="1" ht="49" customHeight="1" spans="1:6">
+      <c r="A6" s="28"/>
+      <c r="B6" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="30"/>
-    </row>
-    <row r="7" s="27" customFormat="1" ht="316" customHeight="1" spans="1:6">
-      <c r="A7" s="29"/>
-      <c r="B7" s="29" t="s">
+      <c r="D6" s="29"/>
+    </row>
+    <row r="7" s="26" customFormat="1" ht="316" customHeight="1" spans="1:6">
+      <c r="A7" s="28"/>
+      <c r="B7" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="30"/>
+      <c r="D7" s="29"/>
     </row>
     <row r="8" customFormat="1" spans="1:6">
       <c r="B8" t="s">
@@ -7205,7 +7203,7 @@
       <c r="C18" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -7234,7 +7232,7 @@
       <c r="E21" s="9"/>
     </row>
     <row r="22" ht="45" spans="2:5">
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="31" t="s">
         <v>47</v>
       </c>
       <c r="C22" s="11" t="s">
@@ -7271,19 +7269,19 @@
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="23" t="s">
         <v>50</v>
       </c>
     </row>
@@ -7305,7 +7303,7 @@
       <c r="B4" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="6" t="s">
         <v>52</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -7515,7 +7513,7 @@
       <c r="D24" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="6" t="s">
         <v>103</v>
       </c>
     </row>
@@ -7534,7 +7532,7 @@
       <c r="C26" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="E26" s="22" t="s">
         <v>108</v>
       </c>
     </row>
@@ -7661,7 +7659,7 @@
         <v>80</v>
       </c>
       <c r="D38" s="15"/>
-      <c r="E38" s="35" t="s">
+      <c r="E38" s="34" t="s">
         <v>130</v>
       </c>
     </row>
@@ -7733,7 +7731,7 @@
       <c r="D45" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="6" t="s">
         <v>147</v>
       </c>
     </row>
@@ -7741,7 +7739,7 @@
       <c r="B46" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="6" t="s">
         <v>149</v>
       </c>
       <c r="D46" s="11" t="s">
@@ -7761,7 +7759,7 @@
       <c r="D47" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="E47" s="25"/>
+      <c r="E47" s="24"/>
     </row>
     <row r="48" customFormat="1" spans="2:6">
       <c r="B48" s="4" t="s">
@@ -7807,7 +7805,7 @@
       <c r="B52" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="C52" s="18" t="s">
+      <c r="C52" s="6" t="s">
         <v>162</v>
       </c>
       <c r="D52" s="11" t="s">
@@ -7882,70 +7880,70 @@
         <v>175</v>
       </c>
       <c r="C59" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D59" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="E59" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="E59" s="18" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="60" ht="255" spans="2:6">
       <c r="B60" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D60" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="F60" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="F60" s="4" t="s">
+    </row>
+    <row r="61" ht="45" spans="2:6">
+      <c r="B61" s="4" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="4" t="s">
+      <c r="C61" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>183</v>
       </c>
       <c r="D61" s="11"/>
       <c r="F61" s="4"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>184</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>185</v>
       </c>
       <c r="D62" s="11"/>
       <c r="F62" s="4"/>
     </row>
     <row r="63" ht="210" spans="2:6">
       <c r="B63" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D63" s="11"/>
       <c r="E63" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F63" s="4"/>
     </row>
     <row r="64" ht="56" customHeight="1" spans="2:6">
       <c r="B64" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D64" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="D64" s="13" t="s">
+      <c r="F64" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="65" ht="43" customHeight="1" spans="2:4">
       <c r="B65" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>57</v>
@@ -7954,30 +7952,30 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="2:4">
       <c r="B66" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C66" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>193</v>
       </c>
       <c r="D66" s="13"/>
     </row>
     <row r="67" spans="2:4">
       <c r="B67" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C67" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="D67" s="15" t="s">
         <v>195</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="68" ht="43" customHeight="1" spans="2:4">
       <c r="B68" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C68" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>198</v>
       </c>
       <c r="D68" s="15"/>
     </row>
@@ -8035,7 +8033,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -8046,7 +8044,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" ht="105" spans="1:7">
@@ -8054,7 +8052,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>53</v>
@@ -8068,7 +8066,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E5" s="9"/>
     </row>
@@ -8077,210 +8075,210 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>203</v>
-      </c>
-      <c r="E6" s="26"/>
+        <v>202</v>
+      </c>
+      <c r="E6" s="25"/>
     </row>
     <row r="7" ht="120" spans="1:7">
       <c r="B7" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="D7" t="s">
         <v>205</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" s="12" t="s">
         <v>206</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>207</v>
       </c>
       <c r="F7" s="4"/>
     </row>
     <row r="8" ht="94" customHeight="1" spans="1:7">
       <c r="B8" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8" t="s">
         <v>208</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="E8" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:7">
       <c r="B9" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C9" t="s">
         <v>212</v>
-      </c>
-      <c r="C9" t="s">
-        <v>213</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" t="s">
         <v>214</v>
-      </c>
-      <c r="C10" t="s">
-        <v>215</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" ht="225" spans="1:7">
       <c r="B11" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C11" t="s">
         <v>216</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>218</v>
-      </c>
       <c r="E11" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="B12" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C12" t="s">
         <v>219</v>
       </c>
-      <c r="C12" t="s">
-        <v>220</v>
-      </c>
       <c r="E12" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="B13" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C13" t="s">
         <v>221</v>
       </c>
-      <c r="C13" t="s">
-        <v>222</v>
-      </c>
       <c r="E13" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:7">
       <c r="B14" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C14" t="s">
         <v>223</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>224</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="15" ht="120" spans="1:7">
       <c r="B15" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="E15" s="9" t="s">
         <v>229</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="16" ht="45" spans="1:7">
       <c r="B16" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C16" t="s">
         <v>231</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>233</v>
       </c>
       <c r="E16" s="9"/>
     </row>
     <row r="17" ht="45" spans="2:6">
       <c r="B17" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C17" t="s">
         <v>234</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="E17" s="9"/>
     </row>
     <row r="18" ht="45" spans="2:6">
       <c r="B18" t="s">
+        <v>236</v>
+      </c>
+      <c r="C18" t="s">
         <v>237</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="D18" s="11" t="s">
-        <v>239</v>
-      </c>
       <c r="E18" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" ht="60" spans="2:6">
       <c r="B19" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C19" t="s">
         <v>240</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>242</v>
-      </c>
       <c r="E19" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="2:6">
       <c r="B20" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C20" t="s">
         <v>243</v>
-      </c>
-      <c r="C20" t="s">
-        <v>244</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="2:6">
       <c r="B21" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="D21" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="4"/>
     </row>
     <row r="22" customFormat="1" ht="60" customHeight="1" spans="2:6">
       <c r="B22" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D22" s="15"/>
       <c r="E22" s="9"/>
@@ -8318,7 +8316,7 @@
       <c r="B1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -8336,7 +8334,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -8347,7 +8345,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" ht="165" spans="1:6">
@@ -8355,11 +8353,11 @@
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" t="s">
         <v>249</v>
-      </c>
-      <c r="D4" t="s">
-        <v>250</v>
       </c>
       <c r="E4" s="9"/>
     </row>
@@ -8380,7 +8378,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -8388,207 +8386,207 @@
     </row>
     <row r="7" ht="165" spans="1:6">
       <c r="B7" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="C7" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="D7" t="s">
         <v>252</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" s="12" t="s">
         <v>253</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="8" ht="71" customHeight="1" spans="1:6">
       <c r="B8" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="E8" s="10"/>
-    </row>
-    <row r="9" ht="30" spans="1:6">
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>259</v>
-      </c>
       <c r="D9" s="11"/>
-      <c r="E9" s="25"/>
+      <c r="E9" s="24"/>
     </row>
     <row r="10" spans="1:6">
       <c r="B10" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>261</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="10"/>
     </row>
-    <row r="11" ht="30" spans="1:6">
+    <row r="11" spans="1:6">
       <c r="B11" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="D11" s="13" t="s">
         <v>263</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="12" ht="60" spans="1:6">
       <c r="B12" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="14" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" ht="33" customHeight="1" spans="1:6">
       <c r="B13" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="D13" s="13"/>
     </row>
     <row r="14" customFormat="1" spans="1:6">
       <c r="B14" t="s">
+        <v>268</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="15" customFormat="1" ht="60" spans="1:6">
       <c r="B15" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C15" t="s">
+        <v>231</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>271</v>
-      </c>
-      <c r="C15" t="s">
-        <v>232</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="16" customFormat="1" ht="30" spans="1:6">
       <c r="B16" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="17" ht="60" spans="2:5">
       <c r="B17" t="s">
+        <v>274</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="11" t="s">
         <v>276</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" t="s">
+        <v>277</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>278</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="19" ht="45" spans="2:5">
       <c r="B19" t="s">
+        <v>279</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="E19" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" t="s">
+        <v>283</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="E20" s="19"/>
+      <c r="E20" s="18"/>
     </row>
     <row r="21" ht="409.5" spans="2:5">
       <c r="B21" t="s">
+        <v>285</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="E21" s="14" t="s">
         <v>287</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="22" ht="60" spans="2:5">
       <c r="B22" t="s">
+        <v>288</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="E22" s="22"/>
+      <c r="E22" s="21"/>
     </row>
     <row r="23" ht="66" customHeight="1" spans="2:5">
       <c r="B23" t="s">
+        <v>290</v>
+      </c>
+      <c r="C23" t="s">
         <v>291</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" s="11" t="s">
         <v>292</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>293</v>
       </c>
       <c r="E23" s="4"/>
     </row>
     <row r="24" customFormat="1" spans="2:5">
       <c r="B24" t="s">
+        <v>293</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>294</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>295</v>
       </c>
       <c r="D24" s="11"/>
       <c r="E24" s="4"/>
     </row>
     <row r="25" customFormat="1" spans="2:5">
       <c r="B25" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="D25" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" customFormat="1" ht="46" customHeight="1" spans="2:5">
       <c r="B26" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D26" s="15"/>
     </row>
@@ -8650,7 +8648,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" ht="90" spans="1:6">
@@ -8658,10 +8656,10 @@
         <v>16</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="D4" t="s">
         <v>299</v>
-      </c>
-      <c r="D4" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
@@ -8674,7 +8672,7 @@
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F5" s="4"/>
     </row>
@@ -8683,7 +8681,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -8691,55 +8689,55 @@
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D7" t="s">
         <v>303</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>305</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="8" ht="63" customHeight="1" spans="1:6">
       <c r="B8" t="s">
+        <v>306</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="D8" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="F8" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" t="s">
+        <v>310</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>312</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="9"/>
     </row>
     <row r="10" ht="30" spans="1:6">
       <c r="B10" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="9"/>
     </row>
     <row r="11" ht="30" spans="1:6">
       <c r="B11" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>138</v>
@@ -8749,51 +8747,51 @@
     </row>
     <row r="12" ht="30" spans="1:6">
       <c r="B12" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>317</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="9"/>
     </row>
     <row r="13" customFormat="1" ht="66" customHeight="1" spans="1:6">
       <c r="B13" t="s">
+        <v>317</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="D13" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>320</v>
-      </c>
       <c r="F13" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:6">
       <c r="B14" t="s">
+        <v>320</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>322</v>
-      </c>
       <c r="D14" s="11"/>
-      <c r="E14" s="22"/>
+      <c r="E14" s="21"/>
     </row>
     <row r="15" customFormat="1" ht="30" spans="1:6">
       <c r="B15" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>324</v>
-      </c>
       <c r="D15" s="11"/>
-      <c r="E15" s="22"/>
+      <c r="E15" s="21"/>
     </row>
     <row r="16" customFormat="1" ht="30" spans="1:6">
       <c r="B16" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>138</v>
@@ -8803,46 +8801,46 @@
     </row>
     <row r="17" customFormat="1" ht="30" spans="2:6">
       <c r="B17" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>327</v>
       </c>
       <c r="D17" s="11"/>
     </row>
     <row r="18" ht="60" spans="2:6">
       <c r="B18" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="D18" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="E18" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="19" ht="93" customHeight="1" spans="2:6">
       <c r="B19" t="s">
+        <v>331</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="F19" s="9" t="s">
         <v>333</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="2:6">
       <c r="B20" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="11"/>
       <c r="F20" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" customFormat="1" ht="120" spans="2:6">
@@ -8851,9 +8849,9 @@
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="E21" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>103</v>
       </c>
       <c r="F21" s="4"/>
@@ -8863,7 +8861,7 @@
         <v>104</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D22" s="11"/>
       <c r="F22" s="4"/>
@@ -8873,11 +8871,11 @@
         <v>106</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D23" s="11"/>
+      <c r="E23" s="22" t="s">
         <v>339</v>
-      </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="23" t="s">
-        <v>340</v>
       </c>
       <c r="F23" s="4"/>
     </row>
@@ -8886,10 +8884,10 @@
         <v>89</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>341</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>342</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -8899,11 +8897,11 @@
         <v>85</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D25" s="11"/>
       <c r="E25" s="14" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F25" s="4"/>
     </row>
@@ -8912,7 +8910,7 @@
         <v>91</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D26" s="11"/>
       <c r="E26" s="4"/>
@@ -8923,7 +8921,7 @@
         <v>93</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D27" s="11"/>
       <c r="E27" s="4"/>
@@ -8934,7 +8932,7 @@
         <v>95</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D28" s="11"/>
       <c r="E28" s="4"/>
@@ -8945,7 +8943,7 @@
         <v>97</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="4"/>
@@ -8956,7 +8954,7 @@
         <v>99</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D30" s="11"/>
       <c r="E30" s="4"/>
@@ -8964,21 +8962,21 @@
     </row>
     <row r="31" customFormat="1" spans="2:6">
       <c r="B31" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="D31" s="15" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" customFormat="1" ht="46" customHeight="1" spans="2:6">
       <c r="B32" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D32" s="15"/>
     </row>
@@ -9031,8 +9029,8 @@
       </c>
     </row>
     <row r="2" ht="45" spans="1:6">
-      <c r="A2" s="21" t="s">
-        <v>352</v>
+      <c r="A2" s="20" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -9041,7 +9039,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" ht="240" spans="1:6">
@@ -9050,10 +9048,10 @@
         <v>16</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D4" t="s">
         <v>354</v>
-      </c>
-      <c r="D4" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -9073,7 +9071,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -9087,155 +9085,155 @@
         <v>58</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" ht="150" spans="1:6">
       <c r="B8" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="D8" t="s">
         <v>358</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" s="12" t="s">
         <v>359</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="9" ht="70" customHeight="1" spans="1:6">
       <c r="B9" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="11" t="s">
         <v>362</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="10" ht="30" spans="1:6">
       <c r="B10" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>365</v>
       </c>
       <c r="D10" s="11"/>
     </row>
     <row r="11" spans="1:6">
       <c r="B11" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="9"/>
     </row>
     <row r="12" ht="30" spans="1:6">
       <c r="B12" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D12" s="11"/>
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:6">
       <c r="B13" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="11" t="s">
         <v>369</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:6">
       <c r="B14" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>371</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>372</v>
       </c>
       <c r="D14" s="11"/>
     </row>
     <row r="15" ht="153" customHeight="1" spans="1:6">
       <c r="B15" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>374</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="16" ht="75" spans="1:6">
       <c r="B16" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C16" t="s">
+        <v>231</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="C16" t="s">
-        <v>232</v>
-      </c>
-      <c r="D16" s="11" t="s">
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="5" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="17" ht="30" spans="2:6">
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="18" ht="90" spans="2:6">
       <c r="B18" t="s">
+        <v>375</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" t="s">
         <v>377</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" s="4" t="s">
         <v>378</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" t="s">
+        <v>379</v>
+      </c>
+      <c r="D19" t="s">
         <v>380</v>
       </c>
-      <c r="D19" t="s">
+      <c r="F19" s="18" t="s">
         <v>381</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="D20" s="15" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1" spans="2:6">
       <c r="B21" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D21" s="15"/>
     </row>
@@ -9289,12 +9287,12 @@
         <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="20"/>
+      <c r="F2" s="19"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1"/>
@@ -9302,7 +9300,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" ht="90" spans="1:6">
@@ -9310,11 +9308,11 @@
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>386</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
@@ -9334,7 +9332,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -9348,262 +9346,262 @@
         <v>58</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" ht="105" spans="1:6">
       <c r="B8" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="D8" t="s">
+        <v>358</v>
+      </c>
+      <c r="E8" s="17" t="s">
         <v>389</v>
-      </c>
-      <c r="D8" t="s">
-        <v>359</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="9" ht="139" customHeight="1" spans="1:6">
       <c r="B9" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>392</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="10" ht="45" spans="1:6">
       <c r="B10" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" ht="210" spans="1:6">
       <c r="B11" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" ht="210" spans="1:6">
       <c r="B12" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="12" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="9" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14" ht="84" customHeight="1" spans="1:6">
       <c r="B14" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:6">
       <c r="B15" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:6">
       <c r="B16" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="10"/>
     </row>
     <row r="17" ht="30" spans="2:6">
       <c r="B17" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="18" ht="105" spans="2:6">
       <c r="B18" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="E18" s="6" t="s">
         <v>403</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="19" ht="30" spans="2:6">
       <c r="B19" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="20" ht="30" spans="2:6">
       <c r="B20" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" ht="37" customHeight="1" spans="2:6">
       <c r="B21" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D21" s="13" t="s">
         <v>407</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>408</v>
       </c>
       <c r="E21" s="9"/>
     </row>
     <row r="22" ht="75" spans="2:6">
       <c r="B22" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="C22" t="s">
         <v>409</v>
-      </c>
-      <c r="C22" t="s">
-        <v>410</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="17" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="23" ht="45" spans="2:6">
       <c r="B23" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="12" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="24" ht="75" spans="2:6">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="24" ht="60" spans="2:6">
       <c r="B24" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C24" t="s">
+        <v>231</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>271</v>
-      </c>
-      <c r="C24" t="s">
-        <v>232</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="25" ht="30" spans="2:6">
       <c r="B25" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="26" ht="45" spans="2:6">
       <c r="B26" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="C26" t="s">
         <v>414</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="27" ht="210" spans="2:6">
       <c r="B27" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" t="s">
-        <v>378</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>417</v>
+        <v>377</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="28" ht="45" spans="2:6">
       <c r="B28" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>418</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" t="s">
+        <v>379</v>
+      </c>
+      <c r="D29" t="s">
         <v>380</v>
-      </c>
-      <c r="D29" t="s">
-        <v>381</v>
       </c>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="D30" s="15" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="31" ht="46" customHeight="1" spans="2:6">
       <c r="B31" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D31" s="15"/>
     </row>
@@ -9659,7 +9657,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -9672,7 +9670,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" ht="180" spans="1:6">
@@ -9681,10 +9679,10 @@
         <v>16</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="D4" t="s">
         <v>422</v>
-      </c>
-      <c r="D4" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
@@ -9704,7 +9702,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -9718,164 +9716,164 @@
         <v>58</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" ht="105" spans="1:6">
       <c r="B8" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="D8" t="s">
+        <v>358</v>
+      </c>
+      <c r="E8" s="17" t="s">
         <v>389</v>
-      </c>
-      <c r="D8" t="s">
-        <v>359</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="9" ht="409" customHeight="1" spans="1:6">
       <c r="B9" s="5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D9" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="10" ht="150" spans="1:6">
       <c r="B10" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D10" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>427</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="11" ht="180" spans="1:6">
       <c r="B11" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C11" s="4"/>
       <c r="E11" s="12" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" ht="150" spans="1:6">
       <c r="B12" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C12" s="4"/>
       <c r="E12" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="13" ht="75" spans="1:6">
       <c r="B13" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C13" t="s">
+        <v>231</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="C13" t="s">
-        <v>232</v>
-      </c>
-      <c r="D13" s="11" t="s">
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" s="5" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="14" ht="30" spans="1:6">
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="15" ht="45" spans="1:6">
       <c r="B15" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="C15" t="s">
         <v>414</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="16" ht="210" spans="1:6">
       <c r="B16" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" t="s">
-        <v>378</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>417</v>
+        <v>377</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="17" ht="45" spans="2:6">
       <c r="B17" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>418</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
+        <v>379</v>
+      </c>
+      <c r="D18" t="s">
         <v>380</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="F18" s="18" t="s">
         <v>381</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="19" ht="165" spans="2:6">
       <c r="B19" t="s">
+        <v>431</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" t="s">
         <v>433</v>
-      </c>
-      <c r="E19" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="D20" s="15" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="21" ht="46" customHeight="1" spans="2:6">
       <c r="B21" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D21" s="15"/>
     </row>

--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - Medent.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - Medent.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Medent" sheetId="11" r:id="rId1"/>
@@ -3322,7 +3322,8 @@
     <t>SHA-256 UUID generated using 
 1. Patient-MRN (the value set for 'identifier (MR) -&gt; value' of Patient Resource from Document.recordTarget.patientRole.id.extension)
 2. Value of the header variable 'X-TechBD-CIN'
-3. Content of first occurance of Document.author section</t>
+3. Content of first occurance of Document.author section
+4. Organization Name from ClinicalDocument.component.structuredBody.component.section[code[@code='46240-8']].entry[1].encounter.participant[@typeCode='LOC'].participantRole[@classCode='SDLOC'].playingEntity.name</t>
   </si>
   <si>
     <t>"id" : "8e4752d52cb9f94657401368f1c8e3cdb052624b10166a665e4c80cdabc62b3c",</t>
@@ -5614,7 +5615,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5622,6 +5622,7 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5629,7 +5630,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5645,7 +5646,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -8651,7 +8652,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="4" ht="90" spans="1:6">
+    <row r="4" ht="165" spans="1:6">
       <c r="B4" t="s">
         <v>16</v>
       </c>
